--- a/analysis/statistics/Within_Flavor_Comparisons.xlsx
+++ b/analysis/statistics/Within_Flavor_Comparisons.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4416" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="5520" uniqueCount="129">
   <si>
     <t>Flavor</t>
   </si>
@@ -388,6 +388,18 @@
   </si>
   <si>
     <t>Effect_Size_Diff</t>
+  </si>
+  <si>
+    <t>x_std_minus_com</t>
+  </si>
+  <si>
+    <t>head_angle_minus_ra</t>
+  </si>
+  <si>
+    <t>iep_minus_ra</t>
+  </si>
+  <si>
+    <t>head_angle_minus_iep</t>
   </si>
 </sst>
 </file>
@@ -436,12 +448,12 @@
   <dimension ref="A1:F274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="true"/>
-    <col min="2" max="2" width="26.28515625" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="16.42578125" customWidth="true"/>
-    <col min="5" max="5" width="13.7109375" customWidth="true"/>
-    <col min="6" max="6" width="8.42578125" customWidth="true"/>
+    <col min="1" max="1" width="26.6640625" customWidth="true"/>
+    <col min="2" max="2" width="23.88671875" customWidth="true"/>
+    <col min="3" max="3" width="15.5546875" customWidth="true"/>
+    <col min="4" max="4" width="15.21875" customWidth="true"/>
+    <col min="5" max="5" width="13.5546875" customWidth="true"/>
+    <col min="6" max="6" width="7.5546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,13 +487,13 @@
         <v>0.79588763277164731</v>
       </c>
       <c r="D2" s="0">
-        <v>0.0235599998998971</v>
+        <v>0.034259503839089656</v>
       </c>
       <c r="E2" s="0">
-        <v>1.5004872294387299</v>
+        <v>1.4965249819105426</v>
       </c>
       <c r="F2" s="0">
-        <v>0.0424</v>
+        <v>0.041599999999999998</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +507,13 @@
         <v>0.44855137977309051</v>
       </c>
       <c r="D3" s="0">
-        <v>-0.27010961139430395</v>
+        <v>-0.29514160818237251</v>
       </c>
       <c r="E3" s="0">
-        <v>1.1606432286397941</v>
+        <v>1.1532336375732992</v>
       </c>
       <c r="F3" s="0">
-        <v>0.2132</v>
+        <v>0.20899999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -515,13 +527,13 @@
         <v>0.010243142500960922</v>
       </c>
       <c r="D4" s="0">
-        <v>-0.5677510962592931</v>
+        <v>-0.56370173724176598</v>
       </c>
       <c r="E4" s="0">
-        <v>0.78879601596496274</v>
+        <v>0.81596797146378009</v>
       </c>
       <c r="F4" s="0">
-        <v>0.94779999999999998</v>
+        <v>0.94240000000000002</v>
       </c>
     </row>
     <row r="5">
@@ -535,13 +547,13 @@
         <v>0.49988405916063744</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.15012157691774103</v>
+        <v>-0.16801396865539814</v>
       </c>
       <c r="E5" s="0">
-        <v>1.0947376740465051</v>
+        <v>1.0947192318089938</v>
       </c>
       <c r="F5" s="0">
-        <v>0.1206</v>
+        <v>0.13039999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -555,13 +567,13 @@
         <v>0.26629021001381986</v>
       </c>
       <c r="D6" s="0">
-        <v>-0.37196117702745107</v>
+        <v>-0.39004378191881273</v>
       </c>
       <c r="E6" s="0">
-        <v>0.81940623969201709</v>
+        <v>0.81629991128546564</v>
       </c>
       <c r="F6" s="0">
-        <v>0.4012</v>
+        <v>0.39340000000000003</v>
       </c>
     </row>
     <row r="7">
@@ -575,13 +587,13 @@
         <v>0.17395982126015738</v>
       </c>
       <c r="D7" s="0">
-        <v>-0.29507134335166962</v>
+        <v>-0.29718847072272714</v>
       </c>
       <c r="E7" s="0">
-        <v>0.82505719648038856</v>
+        <v>0.84198933444685164</v>
       </c>
       <c r="F7" s="0">
-        <v>0.51500000000000001</v>
+        <v>0.49980000000000002</v>
       </c>
     </row>
     <row r="8">
@@ -595,13 +607,13 @@
         <v>0.32047965688763319</v>
       </c>
       <c r="D8" s="0">
-        <v>-0.32782072711825838</v>
+        <v>-0.34979149977740248</v>
       </c>
       <c r="E8" s="0">
-        <v>0.85192360518537757</v>
+        <v>0.82370883556172259</v>
       </c>
       <c r="F8" s="0">
-        <v>0.33839999999999998</v>
+        <v>0.33439999999999998</v>
       </c>
     </row>
     <row r="9">
@@ -615,10 +627,10 @@
         <v>0.7789998348919418</v>
       </c>
       <c r="D9" s="0">
-        <v>0.02656348569242567</v>
+        <v>0.022168867682149651</v>
       </c>
       <c r="E9" s="0">
-        <v>1.4763888897072612</v>
+        <v>1.4527666490120221</v>
       </c>
       <c r="F9" s="0">
         <v>0.043400000000000001</v>
@@ -635,13 +647,13 @@
         <v>0.25227131719384527</v>
       </c>
       <c r="D10" s="0">
-        <v>-0.41523485334848897</v>
+        <v>-0.43668386858443542</v>
       </c>
       <c r="E10" s="0">
-        <v>0.74199732985850031</v>
+        <v>0.74254036621625974</v>
       </c>
       <c r="F10" s="0">
-        <v>0.46239999999999998</v>
+        <v>0.46160000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -655,13 +667,13 @@
         <v>0.31956703971372596</v>
       </c>
       <c r="D11" s="0">
-        <v>-0.33838786590951947</v>
+        <v>-0.3627345249294579</v>
       </c>
       <c r="E11" s="0">
-        <v>0.8043844466519614</v>
+        <v>0.80654496892141991</v>
       </c>
       <c r="F11" s="0">
-        <v>0.34239999999999998</v>
+        <v>0.33679999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -675,13 +687,13 @@
         <v>0.3207548711807095</v>
       </c>
       <c r="D12" s="0">
-        <v>-0.34043697707181031</v>
+        <v>-0.36940479579985047</v>
       </c>
       <c r="E12" s="0">
-        <v>0.8508821505265598</v>
+        <v>0.83625123776623211</v>
       </c>
       <c r="F12" s="0">
-        <v>0.3574</v>
+        <v>0.35599999999999998</v>
       </c>
     </row>
     <row r="13">
@@ -695,13 +707,13 @@
         <v>0.16029955979685406</v>
       </c>
       <c r="D13" s="0">
-        <v>-0.34038042087655035</v>
+        <v>-0.35508521446740526</v>
       </c>
       <c r="E13" s="0">
-        <v>0.90077586557180056</v>
+        <v>0.90010914949005749</v>
       </c>
       <c r="F13" s="0">
-        <v>0.58740000000000003</v>
+        <v>0.58919999999999995</v>
       </c>
     </row>
     <row r="14">
@@ -715,13 +727,13 @@
         <v>0.34776797614389771</v>
       </c>
       <c r="D14" s="0">
-        <v>-0.32932341165304718</v>
+        <v>-0.34699631694388333</v>
       </c>
       <c r="E14" s="0">
-        <v>0.84735489665949104</v>
+        <v>0.8546621563278749</v>
       </c>
       <c r="F14" s="0">
-        <v>0.32279999999999998</v>
+        <v>0.31919999999999998</v>
       </c>
     </row>
     <row r="15">
@@ -735,13 +747,13 @@
         <v>0.34733625299855675</v>
       </c>
       <c r="D15" s="0">
-        <v>-0.32839508630344622</v>
+        <v>-0.31693722032201416</v>
       </c>
       <c r="E15" s="0">
-        <v>0.96622560434632443</v>
+        <v>0.96282792029596298</v>
       </c>
       <c r="F15" s="0">
-        <v>0.33139999999999997</v>
+        <v>0.32879999999999998</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +767,10 @@
         <v>0.80613077527260813</v>
       </c>
       <c r="D16" s="0">
-        <v>0.44536553539250906</v>
+        <v>0.44335434017313624</v>
       </c>
       <c r="E16" s="0">
-        <v>1.3154677528175407</v>
+        <v>1.3141631575117416</v>
       </c>
       <c r="F16" s="0">
         <v>0</v>
@@ -775,13 +787,13 @@
         <v>0.29600357361100982</v>
       </c>
       <c r="D17" s="0">
-        <v>-0.2891034526343168</v>
+        <v>-0.29881773445857163</v>
       </c>
       <c r="E17" s="0">
-        <v>0.87431053430726591</v>
+        <v>0.88043978734046591</v>
       </c>
       <c r="F17" s="0">
-        <v>0.31119999999999998</v>
+        <v>0.31080000000000002</v>
       </c>
     </row>
     <row r="18">
@@ -795,13 +807,13 @@
         <v>0.5295974227578274</v>
       </c>
       <c r="D18" s="0">
-        <v>-0.047462546900700342</v>
+        <v>-0.047749312086210916</v>
       </c>
       <c r="E18" s="0">
-        <v>1.1318393730937046</v>
+        <v>1.1363201092449491</v>
       </c>
       <c r="F18" s="0">
-        <v>0.070400000000000004</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="19">
@@ -815,10 +827,10 @@
         <v>0.96984745403180461</v>
       </c>
       <c r="D19" s="0">
-        <v>0.45964226518797752</v>
+        <v>0.46048827567181222</v>
       </c>
       <c r="E19" s="0">
-        <v>1.5635381399317514</v>
+        <v>1.5664714916379379</v>
       </c>
       <c r="F19" s="0">
         <v>0</v>
@@ -835,13 +847,13 @@
         <v>0.47540797588401407</v>
       </c>
       <c r="D20" s="0">
-        <v>0.021337682131417846</v>
+        <v>0.02974985370361205</v>
       </c>
       <c r="E20" s="0">
-        <v>1.0112328623630447</v>
+        <v>1.0176615367173043</v>
       </c>
       <c r="F20" s="0">
-        <v>0.038800000000000001</v>
+        <v>0.036999999999999998</v>
       </c>
     </row>
     <row r="21">
@@ -855,13 +867,13 @@
         <v>0.016887797879705513</v>
       </c>
       <c r="D21" s="0">
-        <v>-0.60729324339524005</v>
+        <v>-0.61095759301481134</v>
       </c>
       <c r="E21" s="0">
-        <v>0.67043388633508305</v>
+        <v>0.65529940959477973</v>
       </c>
       <c r="F21" s="0">
-        <v>0.96819999999999995</v>
+        <v>0.95860000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -875,10 +887,10 @@
         <v>0.54361631557780199</v>
       </c>
       <c r="D22" s="0">
-        <v>0.19571002173472613</v>
+        <v>0.19848058977418054</v>
       </c>
       <c r="E22" s="0">
-        <v>1.0015264229882226</v>
+        <v>0.9974623327598795</v>
       </c>
       <c r="F22" s="0">
         <v>0.00080000000000000004</v>
@@ -895,13 +907,13 @@
         <v>0.47632059305792129</v>
       </c>
       <c r="D23" s="0">
-        <v>0.116359958329807</v>
+        <v>0.11734932303866824</v>
       </c>
       <c r="E23" s="0">
-        <v>0.95002358293108014</v>
+        <v>0.94990538554306592</v>
       </c>
       <c r="F23" s="0">
-        <v>0.0076</v>
+        <v>0.0061999999999999998</v>
       </c>
     </row>
     <row r="24">
@@ -915,13 +927,13 @@
         <v>0.47513276159093776</v>
       </c>
       <c r="D24" s="0">
-        <v>0.083487256477128957</v>
+        <v>0.083596498135292352</v>
       </c>
       <c r="E24" s="0">
-        <v>0.97577283354273559</v>
+        <v>0.97848266658873939</v>
       </c>
       <c r="F24" s="0">
-        <v>0.017000000000000001</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="25">
@@ -935,10 +947,10 @@
         <v>0.95618719256850127</v>
       </c>
       <c r="D25" s="0">
-        <v>0.63294308373657415</v>
+        <v>0.64100781872081814</v>
       </c>
       <c r="E25" s="0">
-        <v>1.4439274728014908</v>
+        <v>1.433449383467813</v>
       </c>
       <c r="F25" s="0">
         <v>0</v>
@@ -955,13 +967,13 @@
         <v>0.44811965662774955</v>
       </c>
       <c r="D26" s="0">
-        <v>0.10818135033326315</v>
+        <v>0.10936036554353484</v>
       </c>
       <c r="E26" s="0">
-        <v>0.89266270925324132</v>
+        <v>0.89410942274954874</v>
       </c>
       <c r="F26" s="0">
-        <v>0.0083999999999999995</v>
+        <v>0.0080000000000000002</v>
       </c>
     </row>
     <row r="27">
@@ -975,13 +987,13 @@
         <v>0.45879452227405143</v>
       </c>
       <c r="D27" s="0">
-        <v>0.054650986508428062</v>
+        <v>0.05528017325522272</v>
       </c>
       <c r="E27" s="0">
-        <v>1.0376053790371711</v>
+        <v>1.0365339707869021</v>
       </c>
       <c r="F27" s="0">
-        <v>0.023800000000000002</v>
+        <v>0.025000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -995,13 +1007,13 @@
         <v>0.051332679387546931</v>
       </c>
       <c r="D28" s="0">
-        <v>-0.36289960493456747</v>
+        <v>-0.38311718441612314</v>
       </c>
       <c r="E28" s="0">
-        <v>0.359745961067999</v>
+        <v>0.37206461827355181</v>
       </c>
       <c r="F28" s="0">
-        <v>0.74480000000000002</v>
+        <v>0.72660000000000002</v>
       </c>
     </row>
     <row r="29">
@@ -1015,13 +1027,13 @@
         <v>0.18226116975927065</v>
       </c>
       <c r="D29" s="0">
-        <v>-0.077543527562967007</v>
+        <v>-0.082804491959223236</v>
       </c>
       <c r="E29" s="0">
-        <v>0.60555495333017473</v>
+        <v>0.61180639684452187</v>
       </c>
       <c r="F29" s="0">
-        <v>0.17760000000000001</v>
+        <v>0.184</v>
       </c>
     </row>
     <row r="30">
@@ -1035,13 +1047,13 @@
         <v>0.62251120103324786</v>
       </c>
       <c r="D30" s="0">
-        <v>0.13684348957478668</v>
+        <v>0.13715814141593896</v>
       </c>
       <c r="E30" s="0">
-        <v>1.2738463817508245</v>
+        <v>1.2737114326506704</v>
       </c>
       <c r="F30" s="0">
-        <v>0.0112</v>
+        <v>0.010800000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1055,13 +1067,13 @@
         <v>0.12807172288545732</v>
       </c>
       <c r="D31" s="0">
-        <v>-0.13605226476790155</v>
+        <v>-0.13795999205678117</v>
       </c>
       <c r="E31" s="0">
-        <v>0.58161389754834358</v>
+        <v>0.58280093735247496</v>
       </c>
       <c r="F31" s="0">
-        <v>0.38219999999999999</v>
+        <v>0.37919999999999998</v>
       </c>
     </row>
     <row r="32">
@@ -1075,13 +1087,13 @@
         <v>0.33044845511885124</v>
       </c>
       <c r="D32" s="0">
-        <v>-0.44405173910656676</v>
+        <v>-0.44771395442996265</v>
       </c>
       <c r="E32" s="0">
-        <v>1.0613944833367277</v>
+        <v>1.0362566217127771</v>
       </c>
       <c r="F32" s="0">
-        <v>0.38059999999999999</v>
+        <v>0.38740000000000002</v>
       </c>
     </row>
     <row r="33">
@@ -1095,13 +1107,13 @@
         <v>0.19628006257924524</v>
       </c>
       <c r="D33" s="0">
-        <v>-0.10853347232062724</v>
+        <v>-0.11392580190192159</v>
       </c>
       <c r="E33" s="0">
-        <v>0.7168479419490903</v>
+        <v>0.71148303947292524</v>
       </c>
       <c r="F33" s="0">
-        <v>0.24859999999999999</v>
+        <v>0.249</v>
       </c>
     </row>
     <row r="34">
@@ -1115,13 +1127,13 @@
         <v>0.12898434005936454</v>
       </c>
       <c r="D34" s="0">
-        <v>-0.14970397276649841</v>
+        <v>-0.15530526086095237</v>
       </c>
       <c r="E34" s="0">
-        <v>0.62056632755076235</v>
+        <v>0.62361241761090569</v>
       </c>
       <c r="F34" s="0">
-        <v>0.42499999999999999</v>
+        <v>0.42559999999999998</v>
       </c>
     </row>
     <row r="35">
@@ -1135,13 +1147,13 @@
         <v>0.12779650859238101</v>
       </c>
       <c r="D35" s="0">
-        <v>-0.12809476456449515</v>
+        <v>-0.133638355504762</v>
       </c>
       <c r="E35" s="0">
-        <v>0.5899845826651624</v>
+        <v>0.58141202952331173</v>
       </c>
       <c r="F35" s="0">
-        <v>0.379</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="36">
@@ -1155,13 +1167,13 @@
         <v>0.60885093956994463</v>
       </c>
       <c r="D36" s="0">
-        <v>0.11885260826822233</v>
+        <v>0.10738326601851873</v>
       </c>
       <c r="E36" s="0">
-        <v>1.3196608232802718</v>
+        <v>1.3192789961996951</v>
       </c>
       <c r="F36" s="0">
-        <v>0.013599999999999999</v>
+        <v>0.017399999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1175,13 +1187,13 @@
         <v>0.1007834036291928</v>
       </c>
       <c r="D37" s="0">
-        <v>-0.21778582206926636</v>
+        <v>-0.21998813761860425</v>
       </c>
       <c r="E37" s="0">
-        <v>0.61984047319996449</v>
+        <v>0.61976301018793878</v>
       </c>
       <c r="F37" s="0">
-        <v>0.58340000000000003</v>
+        <v>0.58460000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1195,13 +1207,13 @@
         <v>0.51012720166159831</v>
       </c>
       <c r="D38" s="0">
-        <v>0.091840284217981044</v>
+        <v>0.092515031735855846</v>
       </c>
       <c r="E38" s="0">
-        <v>1.0598167164508381</v>
+        <v>1.050454624849144</v>
       </c>
       <c r="F38" s="0">
-        <v>0.016400000000000001</v>
+        <v>0.018599999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1215,13 +1227,13 @@
         <v>0.27653335251478078</v>
       </c>
       <c r="D39" s="0">
-        <v>-0.098670233240858718</v>
+        <v>-0.10226953529028249</v>
       </c>
       <c r="E39" s="0">
-        <v>0.74769751628934356</v>
+        <v>0.74532810130675786</v>
       </c>
       <c r="F39" s="0">
-        <v>0.15060000000000001</v>
+        <v>0.14499999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1235,13 +1247,13 @@
         <v>0.16371667875919646</v>
       </c>
       <c r="D40" s="0">
-        <v>-0.1721957578012106</v>
+        <v>-0.16972201815051507</v>
       </c>
       <c r="E40" s="0">
-        <v>0.47984682552013203</v>
+        <v>0.48706904716297272</v>
       </c>
       <c r="F40" s="0">
-        <v>0.36840000000000001</v>
+        <v>0.36520000000000002</v>
       </c>
     </row>
     <row r="41">
@@ -1255,13 +1267,13 @@
         <v>0.33072279938859411</v>
       </c>
       <c r="D41" s="0">
-        <v>0.0068719687169186139</v>
+        <v>0.0090742530076698413</v>
       </c>
       <c r="E41" s="0">
-        <v>0.68227520564353839</v>
+        <v>0.69110519987074936</v>
       </c>
       <c r="F41" s="0">
-        <v>0.045999999999999999</v>
+        <v>0.0436</v>
       </c>
     </row>
     <row r="42">
@@ -1275,10 +1287,10 @@
         <v>0.78924297739290261</v>
       </c>
       <c r="D42" s="0">
-        <v>0.40553673369384546</v>
+        <v>0.40416666414733754</v>
       </c>
       <c r="E42" s="0">
-        <v>1.3039237400922445</v>
+        <v>1.2909198222609861</v>
       </c>
       <c r="F42" s="0">
         <v>0</v>
@@ -1295,13 +1307,13 @@
         <v>0.26251445969480619</v>
       </c>
       <c r="D43" s="0">
-        <v>-0.015708632592211169</v>
+        <v>-0.023936779966909461</v>
       </c>
       <c r="E43" s="0">
-        <v>0.55917254452312892</v>
+        <v>0.55970534097593838</v>
       </c>
       <c r="F43" s="0">
-        <v>0.063399999999999998</v>
+        <v>0.068199999999999997</v>
       </c>
     </row>
     <row r="44">
@@ -1315,13 +1327,13 @@
         <v>0.32981018221468689</v>
       </c>
       <c r="D44" s="0">
-        <v>0.038467189108598421</v>
+        <v>0.040014640331740042</v>
       </c>
       <c r="E44" s="0">
-        <v>0.63029987557883538</v>
+        <v>0.63874930144100062</v>
       </c>
       <c r="F44" s="0">
-        <v>0.027199999999999999</v>
+        <v>0.028799999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1335,13 +1347,13 @@
         <v>0.33099801368167042</v>
       </c>
       <c r="D45" s="0">
-        <v>0.044057931523801261</v>
+        <v>0.042596636616594297</v>
       </c>
       <c r="E45" s="0">
-        <v>0.63742909140937898</v>
+        <v>0.64479899260107465</v>
       </c>
       <c r="F45" s="0">
-        <v>0.024400000000000002</v>
+        <v>0.025399999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1355,13 +1367,13 @@
         <v>0.15005641729589314</v>
       </c>
       <c r="D46" s="0">
-        <v>-0.15850845697212998</v>
+        <v>-0.16185516479434206</v>
       </c>
       <c r="E46" s="0">
-        <v>0.49051589911788196</v>
+        <v>0.49395440918613442</v>
       </c>
       <c r="F46" s="0">
-        <v>0.35299999999999998</v>
+        <v>0.35420000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1375,13 +1387,13 @@
         <v>0.35801111864485863</v>
       </c>
       <c r="D47" s="0">
-        <v>0.1050625904937906</v>
+        <v>0.1003029155557072</v>
       </c>
       <c r="E47" s="0">
-        <v>0.62843184021996779</v>
+        <v>0.63305857492434781</v>
       </c>
       <c r="F47" s="0">
-        <v>0.0089999999999999993</v>
+        <v>0.0091999999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1395,13 +1407,13 @@
         <v>0.23359384914681758</v>
       </c>
       <c r="D48" s="0">
-        <v>0.06197097867453738</v>
+        <v>0.062239369764868602</v>
       </c>
       <c r="E48" s="0">
-        <v>0.45990936690372042</v>
+        <v>0.46396112559499386</v>
       </c>
       <c r="F48" s="0">
-        <v>0.0086</v>
+        <v>0.0070000000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1415,13 +1427,13 @@
         <v>0.67384388042079479</v>
       </c>
       <c r="D49" s="0">
-        <v>0.24946121326661461</v>
+        <v>0.25194798685491981</v>
       </c>
       <c r="E49" s="0">
-        <v>1.2324330005408495</v>
+        <v>1.2273282417346532</v>
       </c>
       <c r="F49" s="0">
-        <v>0</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="50">
@@ -1435,13 +1447,13 @@
         <v>0.17940440227300425</v>
       </c>
       <c r="D50" s="0">
-        <v>-0.057367449608619114</v>
+        <v>-0.062153266205132951</v>
       </c>
       <c r="E50" s="0">
-        <v>0.5116063329507009</v>
+        <v>0.5094436750317477</v>
       </c>
       <c r="F50" s="0">
-        <v>0.1424</v>
+        <v>0.14580000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -1455,13 +1467,13 @@
         <v>0.27911577573130431</v>
       </c>
       <c r="D51" s="0">
-        <v>-0.44539433828260161</v>
+        <v>-0.43802108651385297</v>
       </c>
       <c r="E51" s="0">
-        <v>0.97532829780056407</v>
+        <v>0.95330287609231523</v>
       </c>
       <c r="F51" s="0">
-        <v>0.40239999999999998</v>
+        <v>0.4128</v>
       </c>
     </row>
     <row r="52">
@@ -1475,13 +1487,13 @@
         <v>0.24761274196679217</v>
       </c>
       <c r="D52" s="0">
-        <v>0.0044282045799528269</v>
+        <v>0.0010275742127770493</v>
       </c>
       <c r="E52" s="0">
-        <v>0.65550341456544148</v>
+        <v>0.65399750423444902</v>
       </c>
       <c r="F52" s="0">
-        <v>0.044600000000000001</v>
+        <v>0.048800000000000003</v>
       </c>
     </row>
     <row r="53">
@@ -1495,13 +1507,13 @@
         <v>0.18031701944691148</v>
       </c>
       <c r="D53" s="0">
-        <v>-0.020243929718745446</v>
+        <v>-0.022822326632195661</v>
       </c>
       <c r="E53" s="0">
-        <v>0.53769408102926974</v>
+        <v>0.53551580716175207</v>
       </c>
       <c r="F53" s="0">
-        <v>0.080600000000000005</v>
+        <v>0.086599999999999997</v>
       </c>
     </row>
     <row r="54">
@@ -1515,13 +1527,13 @@
         <v>0.17912918797992794</v>
       </c>
       <c r="D54" s="0">
-        <v>-0.059129004677280605</v>
+        <v>-0.057793350820729061</v>
       </c>
       <c r="E54" s="0">
-        <v>0.52991542038814388</v>
+        <v>0.52832122379682367</v>
       </c>
       <c r="F54" s="0">
-        <v>0.1356</v>
+        <v>0.14219999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -1535,13 +1547,13 @@
         <v>0.66018361895749145</v>
       </c>
       <c r="D55" s="0">
-        <v>0.20616852847667261</v>
+        <v>0.19660076315022668</v>
       </c>
       <c r="E55" s="0">
-        <v>1.2958665089183001</v>
+        <v>1.3007348672467227</v>
       </c>
       <c r="F55" s="0">
-        <v>0.0030000000000000001</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="56">
@@ -1555,13 +1567,13 @@
         <v>0.15211608301673973</v>
       </c>
       <c r="D56" s="0">
-        <v>-0.097503049932245012</v>
+        <v>-0.10202119942019178</v>
       </c>
       <c r="E56" s="0">
-        <v>0.57299766467797286</v>
+        <v>0.5738573865364649</v>
       </c>
       <c r="F56" s="0">
-        <v>0.28960000000000002</v>
+        <v>0.29139999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1575,13 +1587,13 @@
         <v>0.44025003127397722</v>
       </c>
       <c r="D57" s="0">
-        <v>0.038409956608954604</v>
+        <v>0.044012534592579838</v>
       </c>
       <c r="E57" s="0">
-        <v>0.93264795970847381</v>
+        <v>0.93233342087269078</v>
       </c>
       <c r="F57" s="0">
-        <v>0.033599999999999998</v>
+        <v>0.028799999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -1595,13 +1607,13 @@
         <v>0.05418944687381333</v>
       </c>
       <c r="D58" s="0">
-        <v>-0.13844233205276657</v>
+        <v>-0.14750601558835957</v>
       </c>
       <c r="E58" s="0">
-        <v>0.19000883641461786</v>
+        <v>0.1902304924948881</v>
       </c>
       <c r="F58" s="0">
-        <v>0.51859999999999995</v>
+        <v>0.51839999999999997</v>
       </c>
     </row>
     <row r="59">
@@ -1615,13 +1627,13 @@
         <v>0.51270962487812188</v>
       </c>
       <c r="D59" s="0">
-        <v>-0.10644799936690319</v>
+        <v>-0.12602268567874225</v>
       </c>
       <c r="E59" s="0">
-        <v>1.1602110398172782</v>
+        <v>1.1409907521511569</v>
       </c>
       <c r="F59" s="0">
-        <v>0.0964</v>
+        <v>0.1066</v>
       </c>
     </row>
     <row r="60">
@@ -1635,13 +1647,13 @@
         <v>0.014018892819974593</v>
       </c>
       <c r="D60" s="0">
-        <v>-0.20399748577811749</v>
+        <v>-0.20864537112822959</v>
       </c>
       <c r="E60" s="0">
-        <v>0.34126050157976417</v>
+        <v>0.34172663525869063</v>
       </c>
       <c r="F60" s="0">
-        <v>0.92859999999999998</v>
+        <v>0.94340000000000002</v>
       </c>
     </row>
     <row r="61">
@@ -1655,13 +1667,13 @@
         <v>0.053276829699906103</v>
       </c>
       <c r="D61" s="0">
-        <v>-0.22911639324611482</v>
+        <v>-0.23113448484237575</v>
       </c>
       <c r="E61" s="0">
-        <v>0.23172809468819783</v>
+        <v>0.23670986340021971</v>
       </c>
       <c r="F61" s="0">
-        <v>0.62639999999999996</v>
+        <v>0.62260000000000004</v>
       </c>
     </row>
     <row r="62">
@@ -1675,13 +1687,13 @@
         <v>0.054464661166889639</v>
       </c>
       <c r="D62" s="0">
-        <v>-0.18302177147447352</v>
+        <v>-0.18560714803166806</v>
       </c>
       <c r="E62" s="0">
-        <v>0.19750678891030343</v>
+        <v>0.19748374483871889</v>
       </c>
       <c r="F62" s="0">
-        <v>0.5706</v>
+        <v>0.5716</v>
       </c>
     </row>
     <row r="63">
@@ -1695,13 +1707,13 @@
         <v>0.42658976981067392</v>
       </c>
       <c r="D63" s="0">
-        <v>0.02551493166817953</v>
+        <v>0.015829069354795916</v>
       </c>
       <c r="E63" s="0">
-        <v>0.97063457035690259</v>
+        <v>0.97166824055734469</v>
       </c>
       <c r="F63" s="0">
-        <v>0.0356</v>
+        <v>0.040800000000000003</v>
       </c>
     </row>
     <row r="64">
@@ -1715,13 +1727,13 @@
         <v>0.081477766130077845</v>
       </c>
       <c r="D64" s="0">
-        <v>-0.26721179991464106</v>
+        <v>-0.26966150525371446</v>
       </c>
       <c r="E64" s="0">
-        <v>0.3200781799869511</v>
+        <v>0.32215171329275749</v>
       </c>
       <c r="F64" s="0">
-        <v>0.57120000000000004</v>
+        <v>0.56940000000000002</v>
       </c>
     </row>
     <row r="65">
@@ -1735,13 +1747,13 @@
         <v>0.49443947814779055</v>
       </c>
       <c r="D65" s="0">
-        <v>0.089129726720603569</v>
+        <v>0.099145846699958073</v>
       </c>
       <c r="E65" s="0">
-        <v>0.92428484590106241</v>
+        <v>0.9186718414323346</v>
       </c>
       <c r="F65" s="0">
-        <v>0.017999999999999999</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="66">
@@ -1755,10 +1767,10 @@
         <v>0.9529596561520991</v>
       </c>
       <c r="D66" s="0">
-        <v>0.6022709225112407</v>
+        <v>0.59521743702551999</v>
       </c>
       <c r="E66" s="0">
-        <v>1.4254965868952676</v>
+        <v>1.4260306377107321</v>
       </c>
       <c r="F66" s="0">
         <v>0</v>
@@ -1775,13 +1787,13 @@
         <v>0.42623113845400262</v>
       </c>
       <c r="D67" s="0">
-        <v>0.051134252987530826</v>
+        <v>0.056016569618784512</v>
       </c>
       <c r="E67" s="0">
-        <v>0.79106730894520449</v>
+        <v>0.79109765961871925</v>
       </c>
       <c r="F67" s="0">
-        <v>0.026599999999999999</v>
+        <v>0.0246</v>
       </c>
     </row>
     <row r="68">
@@ -1795,13 +1807,13 @@
         <v>0.49352686097388332</v>
       </c>
       <c r="D68" s="0">
-        <v>0.13317764426034354</v>
+        <v>0.13981641030358513</v>
       </c>
       <c r="E68" s="0">
-        <v>0.85508529313935955</v>
+        <v>0.85947087327831406</v>
       </c>
       <c r="F68" s="0">
-        <v>0.0077999999999999997</v>
+        <v>0.0080000000000000002</v>
       </c>
     </row>
     <row r="69">
@@ -1815,13 +1827,13 @@
         <v>0.49471469244086686</v>
       </c>
       <c r="D69" s="0">
-        <v>0.11027061008288386</v>
+        <v>0.11475964780775116</v>
       </c>
       <c r="E69" s="0">
-        <v>0.89361788815297127</v>
+        <v>0.88586584684957403</v>
       </c>
       <c r="F69" s="0">
-        <v>0.012200000000000001</v>
+        <v>0.0124</v>
       </c>
     </row>
     <row r="70">
@@ -1835,13 +1847,13 @@
         <v>0.013660261463303319</v>
       </c>
       <c r="D70" s="0">
-        <v>-0.43605505074842299</v>
+        <v>-0.43773906091380532</v>
       </c>
       <c r="E70" s="0">
-        <v>0.37284104443407451</v>
+        <v>0.38107266575997523</v>
       </c>
       <c r="F70" s="0">
-        <v>0.98219999999999996</v>
+        <v>0.96340000000000003</v>
       </c>
     </row>
     <row r="71">
@@ -1855,10 +1867,10 @@
         <v>0.52172779740405506</v>
       </c>
       <c r="D71" s="0">
-        <v>0.15274727295656532</v>
+        <v>0.15690481019197269</v>
       </c>
       <c r="E71" s="0">
-        <v>0.89030719644514922</v>
+        <v>0.88682025940680842</v>
       </c>
       <c r="F71" s="0">
         <v>0.0070000000000000001</v>
@@ -1875,13 +1887,13 @@
         <v>0.45852017800430855</v>
       </c>
       <c r="D72" s="0">
-        <v>-0.07237134753255059</v>
+        <v>-0.094631447977873262</v>
       </c>
       <c r="E72" s="0">
-        <v>1.0842583109659343</v>
+        <v>1.0592396304899174</v>
       </c>
       <c r="F72" s="0">
-        <v>0.093200000000000005</v>
+        <v>0.099000000000000005</v>
       </c>
     </row>
     <row r="73">
@@ -1895,13 +1907,13 @@
         <v>0.068208339693787923</v>
       </c>
       <c r="D73" s="0">
-        <v>-0.099569508355660197</v>
+        <v>-0.10222412531922695</v>
       </c>
       <c r="E73" s="0">
-        <v>0.25585905685798854</v>
+        <v>0.25727375835090238</v>
       </c>
       <c r="F73" s="0">
-        <v>0.43940000000000001</v>
+        <v>0.4506</v>
       </c>
     </row>
     <row r="74">
@@ -1915,13 +1927,13 @@
         <v>0.00091261717390722641</v>
       </c>
       <c r="D74" s="0">
-        <v>-0.1481821241371693</v>
+        <v>-0.15295511388962269</v>
       </c>
       <c r="E74" s="0">
-        <v>0.16009279469386251</v>
+        <v>0.15966507666752256</v>
       </c>
       <c r="F74" s="0">
-        <v>0.99039999999999995</v>
+        <v>0.98899999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -1935,13 +1947,13 @@
         <v>0.00027521429307630907</v>
       </c>
       <c r="D75" s="0">
-        <v>-0.089512607186540361</v>
+        <v>-0.087754369929432308</v>
       </c>
       <c r="E75" s="0">
-        <v>0.073446472137233765</v>
+        <v>0.074573399401723139</v>
       </c>
       <c r="F75" s="0">
-        <v>0.98080000000000001</v>
+        <v>0.9748</v>
       </c>
     </row>
     <row r="76">
@@ -1955,13 +1967,13 @@
         <v>0.48077921668448725</v>
       </c>
       <c r="D76" s="0">
-        <v>0.15339243968339378</v>
+        <v>0.14080484800180937</v>
       </c>
       <c r="E76" s="0">
-        <v>0.90188941253264832</v>
+        <v>0.90169819321085365</v>
       </c>
       <c r="F76" s="0">
-        <v>0.0030000000000000001</v>
+        <v>0.0054000000000000003</v>
       </c>
     </row>
     <row r="77">
@@ -1975,13 +1987,13 @@
         <v>0.027288319256264515</v>
       </c>
       <c r="D77" s="0">
-        <v>-0.17271894640748281</v>
+        <v>-0.17463537419776448</v>
       </c>
       <c r="E77" s="0">
-        <v>0.21817651475059113</v>
+        <v>0.2244855168727517</v>
       </c>
       <c r="F77" s="0">
-        <v>0.79700000000000004</v>
+        <v>0.79020000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -1995,13 +2007,13 @@
         <v>0.52672851769809648</v>
       </c>
       <c r="D78" s="0">
-        <v>0.063504781210851013</v>
+        <v>0.05209931664243822</v>
       </c>
       <c r="E78" s="0">
-        <v>1.1065423246441148</v>
+        <v>1.1087759293411996</v>
       </c>
       <c r="F78" s="0">
-        <v>0.026200000000000001</v>
+        <v>0.030200000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -2015,13 +2027,13 @@
         <v>0.45943279517821578</v>
       </c>
       <c r="D79" s="0">
-        <v>-0.022828379382486108</v>
+        <v>-0.030243245797282936</v>
       </c>
       <c r="E79" s="0">
-        <v>1.0558358904259384</v>
+        <v>1.0452770349562317</v>
       </c>
       <c r="F79" s="0">
-        <v>0.062600000000000003</v>
+        <v>0.065799999999999997</v>
       </c>
     </row>
     <row r="80">
@@ -2035,13 +2047,13 @@
         <v>0.45824496371123225</v>
       </c>
       <c r="D80" s="0">
-        <v>-0.042099860759861496</v>
+        <v>-0.060029566180442195</v>
       </c>
       <c r="E80" s="0">
-        <v>1.0556954179666178</v>
+        <v>1.0369648377906495</v>
       </c>
       <c r="F80" s="0">
-        <v>0.0746</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="81">
@@ -2055,10 +2067,10 @@
         <v>0.93929939468879575</v>
       </c>
       <c r="D81" s="0">
-        <v>0.56199099682510778</v>
+        <v>0.55870847343024721</v>
       </c>
       <c r="E81" s="0">
-        <v>1.4789513322436454</v>
+        <v>1.4781409950231366</v>
       </c>
       <c r="F81" s="0">
         <v>0</v>
@@ -2075,13 +2087,13 @@
         <v>0.43123185874804404</v>
       </c>
       <c r="D82" s="0">
-        <v>-0.01604999518758754</v>
+        <v>-0.027246241336128907</v>
       </c>
       <c r="E82" s="0">
-        <v>0.99593785949338942</v>
+        <v>0.98692676049624995</v>
       </c>
       <c r="F82" s="0">
-        <v>0.062199999999999998</v>
+        <v>0.063799999999999996</v>
       </c>
     </row>
     <row r="83">
@@ -2095,13 +2107,13 @@
         <v>0.067295722519880696</v>
       </c>
       <c r="D83" s="0">
-        <v>-0.003018293867512345</v>
+        <v>-0.0027859856032663166</v>
       </c>
       <c r="E83" s="0">
-        <v>0.1453582448011872</v>
+        <v>0.14840117092042276</v>
       </c>
       <c r="F83" s="0">
-        <v>0.057599999999999999</v>
+        <v>0.060400000000000002</v>
       </c>
     </row>
     <row r="84">
@@ -2115,13 +2127,13 @@
         <v>0.068483553986864232</v>
       </c>
       <c r="D84" s="0">
-        <v>-0.076104283659485239</v>
+        <v>-0.076949609187631524</v>
       </c>
       <c r="E84" s="0">
-        <v>0.22040500023952192</v>
+        <v>0.22392363777282354</v>
       </c>
       <c r="F84" s="0">
-        <v>0.36059999999999998</v>
+        <v>0.35620000000000002</v>
       </c>
     </row>
     <row r="85">
@@ -2135,13 +2147,13 @@
         <v>0.41257087699069933</v>
       </c>
       <c r="D85" s="0">
-        <v>0.15202592109407959</v>
+        <v>0.14659266935232149</v>
       </c>
       <c r="E85" s="0">
-        <v>0.72759571356969244</v>
+        <v>0.7200059281002702</v>
       </c>
       <c r="F85" s="0">
-        <v>0.0022000000000000001</v>
+        <v>0.0040000000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -2155,13 +2167,13 @@
         <v>0.095496658950052438</v>
       </c>
       <c r="D86" s="0">
-        <v>0.038621401292066038</v>
+        <v>0.038056831449279627</v>
       </c>
       <c r="E86" s="0">
-        <v>0.16234877781231685</v>
+        <v>0.16138514876862919</v>
       </c>
       <c r="F86" s="0">
-        <v>0.0011999999999999999</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="87">
@@ -2175,13 +2187,13 @@
         <v>0.0011878314669835355</v>
       </c>
       <c r="D87" s="0">
-        <v>-0.12402398513540297</v>
+        <v>-0.12393713276332904</v>
       </c>
       <c r="E87" s="0">
-        <v>0.12630329408390162</v>
+        <v>0.12661867989788306</v>
       </c>
       <c r="F87" s="0">
-        <v>0.99939999999999996</v>
+        <v>0.98860000000000003</v>
       </c>
     </row>
     <row r="88">
@@ -2195,13 +2207,13 @@
         <v>0.47986659951058003</v>
       </c>
       <c r="D88" s="0">
-        <v>0.18728610025502881</v>
+        <v>0.1796917390646616</v>
       </c>
       <c r="E88" s="0">
-        <v>0.81836546211648575</v>
+        <v>0.82169248354225699</v>
       </c>
       <c r="F88" s="0">
-        <v>0.0014</v>
+        <v>0.0025999999999999999</v>
       </c>
     </row>
     <row r="89">
@@ -2215,13 +2227,13 @@
         <v>0.028200936430171741</v>
       </c>
       <c r="D89" s="0">
-        <v>-0.068725717626429372</v>
+        <v>-0.071480993136517346</v>
       </c>
       <c r="E89" s="0">
-        <v>0.11946021397275736</v>
+        <v>0.11870282994925829</v>
       </c>
       <c r="F89" s="0">
-        <v>0.54559999999999997</v>
+        <v>0.53859999999999997</v>
       </c>
     </row>
     <row r="90">
@@ -2235,13 +2247,13 @@
         <v>0.48105443097756356</v>
       </c>
       <c r="D90" s="0">
-        <v>0.17317569625041157</v>
+        <v>0.16570185077828864</v>
       </c>
       <c r="E90" s="0">
-        <v>0.8567380946801868</v>
+        <v>0.86175585262606092</v>
       </c>
       <c r="F90" s="0">
-        <v>0.0011999999999999999</v>
+        <v>0.0035999999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -2255,13 +2267,13 @@
         <v>0.027013104963188206</v>
       </c>
       <c r="D91" s="0">
-        <v>-0.13389494282561332</v>
+        <v>-0.13252666547216552</v>
       </c>
       <c r="E91" s="0">
-        <v>0.18786898057785179</v>
+        <v>0.18874244612923979</v>
       </c>
       <c r="F91" s="0">
-        <v>0.72199999999999998</v>
+        <v>0.71819999999999995</v>
       </c>
     </row>
     <row r="92">
@@ -2275,13 +2287,13 @@
         <v>0.50806753594075182</v>
       </c>
       <c r="D92" s="0">
-        <v>0.2498670144579854</v>
+        <v>0.24128177623461453</v>
       </c>
       <c r="E92" s="0">
-        <v>0.81893528104718849</v>
+        <v>0.81686030604782445</v>
       </c>
       <c r="F92" s="0">
-        <v>0</v>
+        <v>0.00080000000000000004</v>
       </c>
     </row>
     <row r="93">
@@ -2295,13 +2307,13 @@
         <v>0.87428709001512872</v>
       </c>
       <c r="D93" s="0">
-        <v>0.18111636634482453</v>
+        <v>0.17222913255947675</v>
       </c>
       <c r="E93" s="0">
-        <v>1.384410508854169</v>
+        <v>1.3843701069129182</v>
       </c>
       <c r="F93" s="0">
-        <v>0.010999999999999999</v>
+        <v>0.012800000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -2315,13 +2327,13 @@
         <v>0.63197843812478027</v>
       </c>
       <c r="D94" s="0">
-        <v>-0.051645733228398438</v>
+        <v>-0.078513678966049327</v>
       </c>
       <c r="E94" s="0">
-        <v>1.3921980672440346</v>
+        <v>1.3801636993311539</v>
       </c>
       <c r="F94" s="0">
-        <v>0.071800000000000003</v>
+        <v>0.080600000000000005</v>
       </c>
     </row>
     <row r="95">
@@ -2335,13 +2347,13 @@
         <v>0.16708768054776491</v>
       </c>
       <c r="D95" s="0">
-        <v>-0.590184075422165</v>
+        <v>-0.60592648526653137</v>
       </c>
       <c r="E95" s="0">
-        <v>0.65814675041386317</v>
+        <v>0.64903449024825566</v>
       </c>
       <c r="F95" s="0">
-        <v>0.73680000000000001</v>
+        <v>0.73799999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -2355,13 +2367,13 @@
         <v>0.65403852789981554</v>
       </c>
       <c r="D96" s="0">
-        <v>0.017219479573158836</v>
+        <v>-0.0031826167372125402</v>
       </c>
       <c r="E96" s="0">
-        <v>1.2575174228558215</v>
+        <v>1.2441029132548478</v>
       </c>
       <c r="F96" s="0">
-        <v>0.0436</v>
+        <v>0.051799999999999999</v>
       </c>
     </row>
     <row r="97">
@@ -2375,13 +2387,13 @@
         <v>0.41967935625216879</v>
       </c>
       <c r="D97" s="0">
-        <v>-0.22745523104371662</v>
+        <v>-0.249662357344481</v>
       </c>
       <c r="E97" s="0">
-        <v>0.92146580718035298</v>
+        <v>0.90849396618280187</v>
       </c>
       <c r="F97" s="0">
-        <v>0.22359999999999999</v>
+        <v>0.23039999999999999</v>
       </c>
     </row>
     <row r="98">
@@ -2409,13 +2421,13 @@
         <v>0.39123442392841346</v>
       </c>
       <c r="D99" s="0">
-        <v>-0.25627501688929472</v>
+        <v>-0.27995481174957604</v>
       </c>
       <c r="E99" s="0">
-        <v>0.89347077727634616</v>
+        <v>0.87798000434811518</v>
       </c>
       <c r="F99" s="0">
-        <v>0.26479999999999998</v>
+        <v>0.27079999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -2429,13 +2441,13 @@
         <v>0.8786423978462663</v>
       </c>
       <c r="D100" s="0">
-        <v>0.17760886039173052</v>
+        <v>0.1779192778546192</v>
       </c>
       <c r="E100" s="0">
-        <v>1.5326623671650395</v>
+        <v>1.5007341015541487</v>
       </c>
       <c r="F100" s="0">
-        <v>0.0077999999999999997</v>
+        <v>0.0080000000000000002</v>
       </c>
     </row>
     <row r="101">
@@ -2446,16 +2458,16 @@
         <v>13</v>
       </c>
       <c r="C101" s="0">
-        <v>0.10984536566046371</v>
+        <v>0.41139780138808713</v>
       </c>
       <c r="D101" s="0">
-        <v>-0.58587643539215661</v>
+        <v>-0.26311570263926387</v>
       </c>
       <c r="E101" s="0">
-        <v>0.54503577502275225</v>
+        <v>0.89144104336495089</v>
       </c>
       <c r="F101" s="0">
-        <v>0.83899999999999997</v>
+        <v>0.25180000000000002</v>
       </c>
     </row>
     <row r="102">
@@ -2466,16 +2478,16 @@
         <v>14</v>
       </c>
       <c r="C102" s="0">
-        <v>0.13917191528128853</v>
+        <v>0.40167738577917012</v>
       </c>
       <c r="D102" s="0">
-        <v>-0.55706038033240879</v>
+        <v>-0.26731262163449743</v>
       </c>
       <c r="E102" s="0">
-        <v>0.57941470312225229</v>
+        <v>0.86525531780566423</v>
       </c>
       <c r="F102" s="0">
-        <v>0.76939999999999997</v>
+        <v>0.25800000000000001</v>
       </c>
     </row>
     <row r="103">
@@ -2486,16 +2498,16 @@
         <v>15</v>
       </c>
       <c r="C103" s="0">
-        <v>0.01394968777205019</v>
+        <v>0.36207143085879123</v>
       </c>
       <c r="D103" s="0">
-        <v>-0.68071436741659119</v>
+        <v>-0.31068846984773468</v>
       </c>
       <c r="E103" s="0">
-        <v>0.43790400035366611</v>
+        <v>0.82529013723075617</v>
       </c>
       <c r="F103" s="0">
-        <v>0.91739999999999999</v>
+        <v>0.31419999999999998</v>
       </c>
     </row>
     <row r="104">
@@ -2506,16 +2518,16 @@
         <v>16</v>
       </c>
       <c r="C104" s="0">
-        <v>0.064955919953540942</v>
+        <v>0.24168986395839209</v>
       </c>
       <c r="D104" s="0">
-        <v>-0.59503487310625802</v>
+        <v>-0.42472760553584687</v>
       </c>
       <c r="E104" s="0">
-        <v>0.46285782396528075</v>
+        <v>0.64525887682127658</v>
       </c>
       <c r="F104" s="0">
-        <v>0.92759999999999998</v>
+        <v>0.51819999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -2543,13 +2555,13 @@
         <v>0.24230865189034845</v>
       </c>
       <c r="D106" s="0">
-        <v>-0.54203171970116582</v>
+        <v>-0.51980489730825008</v>
       </c>
       <c r="E106" s="0">
-        <v>0.76672474682490965</v>
+        <v>0.75828836391683252</v>
       </c>
       <c r="F106" s="0">
-        <v>0.58220000000000005</v>
+        <v>0.57440000000000002</v>
       </c>
     </row>
     <row r="107">
@@ -2563,10 +2575,10 @@
         <v>0.70719940946736382</v>
       </c>
       <c r="D107" s="0">
-        <v>0.39031379164313618</v>
+        <v>0.39754150856907888</v>
       </c>
       <c r="E107" s="0">
-        <v>1.1092712914626066</v>
+        <v>1.119762148150206</v>
       </c>
       <c r="F107" s="0">
         <v>0</v>
@@ -2583,13 +2595,13 @@
         <v>0.22024856211531318</v>
       </c>
       <c r="D108" s="0">
-        <v>-0.40668697520311614</v>
+        <v>-0.39989645869220125</v>
       </c>
       <c r="E108" s="0">
-        <v>0.71202487937041437</v>
+        <v>0.71677504972106498</v>
       </c>
       <c r="F108" s="0">
-        <v>0.43419999999999998</v>
+        <v>0.44700000000000001</v>
       </c>
     </row>
     <row r="109">
@@ -2603,13 +2615,13 @@
         <v>0.45460773376295993</v>
       </c>
       <c r="D109" s="0">
-        <v>0.012915594711205292</v>
+        <v>0.015523939185163704</v>
       </c>
       <c r="E109" s="0">
-        <v>0.89324770033138701</v>
+        <v>0.89725564751980902</v>
       </c>
       <c r="F109" s="0">
-        <v>0.043799999999999999</v>
+        <v>0.041799999999999997</v>
       </c>
     </row>
     <row r="110">
@@ -2637,13 +2649,13 @@
         <v>0.48305266608671527</v>
       </c>
       <c r="D111" s="0">
-        <v>0.073996891080659322</v>
+        <v>0.079043769469070768</v>
       </c>
       <c r="E111" s="0">
-        <v>0.91614169306625959</v>
+        <v>0.92062517648388009</v>
       </c>
       <c r="F111" s="0">
-        <v>0.021399999999999999</v>
+        <v>0.019400000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -2657,13 +2669,13 @@
         <v>0.0043553078311375781</v>
       </c>
       <c r="D112" s="0">
-        <v>-0.510207955876403</v>
+        <v>-0.52378900973888409</v>
       </c>
       <c r="E112" s="0">
-        <v>0.57808634046587004</v>
+        <v>0.57408347828464179</v>
       </c>
       <c r="F112" s="0">
-        <v>0.96460000000000001</v>
+        <v>0.98040000000000005</v>
       </c>
     </row>
     <row r="113">
@@ -2674,16 +2686,16 @@
         <v>25</v>
       </c>
       <c r="C113" s="0">
-        <v>0.76444172435466507</v>
+        <v>0.4628892886270416</v>
       </c>
       <c r="D113" s="0">
-        <v>0.40614767535230123</v>
+        <v>0.10980576484731008</v>
       </c>
       <c r="E113" s="0">
-        <v>1.2072600419082062</v>
+        <v>0.86425660538628646</v>
       </c>
       <c r="F113" s="0">
-        <v>0</v>
+        <v>0.0094000000000000004</v>
       </c>
     </row>
     <row r="114">
@@ -2694,16 +2706,16 @@
         <v>26</v>
       </c>
       <c r="C114" s="0">
-        <v>0.73511517473384025</v>
+        <v>0.47260970423595861</v>
       </c>
       <c r="D114" s="0">
-        <v>0.37361734345549202</v>
+        <v>0.12839851466893632</v>
       </c>
       <c r="E114" s="0">
-        <v>1.1807336422084871</v>
+        <v>0.86232894628087564</v>
       </c>
       <c r="F114" s="0">
-        <v>0</v>
+        <v>0.0056</v>
       </c>
     </row>
     <row r="115">
@@ -2714,16 +2726,16 @@
         <v>27</v>
       </c>
       <c r="C115" s="0">
-        <v>0.86033740224307853</v>
+        <v>0.51221565915633749</v>
       </c>
       <c r="D115" s="0">
-        <v>0.49954424109196865</v>
+        <v>0.15558315353680685</v>
       </c>
       <c r="E115" s="0">
-        <v>1.3045036246504376</v>
+        <v>0.9222717531105834</v>
       </c>
       <c r="F115" s="0">
-        <v>0</v>
+        <v>0.0041999999999999998</v>
       </c>
     </row>
     <row r="116">
@@ -2734,13 +2746,13 @@
         <v>28</v>
       </c>
       <c r="C116" s="0">
-        <v>0.80933117006158772</v>
+        <v>0.63259722605673663</v>
       </c>
       <c r="D116" s="0">
-        <v>0.47914904563584121</v>
+        <v>0.30234605573850648</v>
       </c>
       <c r="E116" s="0">
-        <v>1.2329259332882825</v>
+        <v>1.053542832522167</v>
       </c>
       <c r="F116" s="0">
         <v>0</v>
@@ -2771,13 +2783,13 @@
         <v>0.46489075757701537</v>
       </c>
       <c r="D118" s="0">
-        <v>0.13811305133804441</v>
+        <v>0.15087955367200129</v>
       </c>
       <c r="E118" s="0">
-        <v>1.1529501881676336</v>
+        <v>1.1380950675485844</v>
       </c>
       <c r="F118" s="0">
-        <v>0.0044000000000000003</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="119">
@@ -2791,13 +2803,13 @@
         <v>0.022060089775035263</v>
       </c>
       <c r="D119" s="0">
-        <v>-0.55232326704193935</v>
+        <v>-0.54748301895671947</v>
       </c>
       <c r="E119" s="0">
-        <v>0.39014929558567835</v>
+        <v>0.39201071046591851</v>
       </c>
       <c r="F119" s="0">
-        <v>0.96220000000000006</v>
+        <v>0.95860000000000001</v>
       </c>
     </row>
     <row r="120">
@@ -2811,13 +2823,13 @@
         <v>0.21229908187261148</v>
       </c>
       <c r="D120" s="0">
-        <v>-0.047053021937342565</v>
+        <v>-0.045082543324995006</v>
       </c>
       <c r="E120" s="0">
-        <v>0.80322294721951537</v>
+        <v>0.7934187778302918</v>
       </c>
       <c r="F120" s="0">
-        <v>0.10299999999999999</v>
+        <v>0.099599999999999994</v>
       </c>
     </row>
     <row r="121">
@@ -2845,13 +2857,13 @@
         <v>0.24074401419636682</v>
       </c>
       <c r="D122" s="0">
-        <v>-0.04590784122774863</v>
+        <v>-0.040786372687756478</v>
       </c>
       <c r="E122" s="0">
-        <v>0.85453480655835712</v>
+        <v>0.84124104044968462</v>
       </c>
       <c r="F122" s="0">
-        <v>0.0964</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -2865,13 +2877,13 @@
         <v>0.24666395972148603</v>
       </c>
       <c r="D123" s="0">
-        <v>-0.61214514562978284</v>
+        <v>-0.5975080426748548</v>
       </c>
       <c r="E123" s="0">
-        <v>0.97648119387020249</v>
+        <v>0.96208390098370722</v>
       </c>
       <c r="F123" s="0">
-        <v>0.63759999999999995</v>
+        <v>0.64800000000000002</v>
       </c>
     </row>
     <row r="124">
@@ -2882,16 +2894,16 @@
         <v>36</v>
       </c>
       <c r="C124" s="0">
-        <v>0.52213307246431651</v>
+        <v>0.22058063673669315</v>
       </c>
       <c r="D124" s="0">
-        <v>0.17898741143942826</v>
+        <v>-0.05346488870918864</v>
       </c>
       <c r="E124" s="0">
-        <v>1.2033382603569751</v>
+        <v>0.82628122543088578</v>
       </c>
       <c r="F124" s="0">
-        <v>0.0030000000000000001</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="125">
@@ -2902,16 +2914,16 @@
         <v>37</v>
       </c>
       <c r="C125" s="0">
-        <v>0.49280652284349175</v>
+        <v>0.23030105234561016</v>
       </c>
       <c r="D125" s="0">
-        <v>0.15481489637990561</v>
+        <v>-0.033549286290179781</v>
       </c>
       <c r="E125" s="0">
-        <v>1.1703392100612993</v>
+        <v>0.83724022300897927</v>
       </c>
       <c r="F125" s="0">
-        <v>0.0038</v>
+        <v>0.095399999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -2922,16 +2934,16 @@
         <v>38</v>
       </c>
       <c r="C126" s="0">
-        <v>0.61802875035273008</v>
+        <v>0.26990700726598904</v>
       </c>
       <c r="D126" s="0">
-        <v>0.25551175569482704</v>
+        <v>0.0014787581289992802</v>
       </c>
       <c r="E126" s="0">
-        <v>1.3139636940961998</v>
+        <v>0.875144103774529</v>
       </c>
       <c r="F126" s="0">
-        <v>0.0011999999999999999</v>
+        <v>0.048000000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -2942,16 +2954,16 @@
         <v>39</v>
       </c>
       <c r="C127" s="0">
-        <v>0.56702251817123939</v>
+        <v>0.39028857416638818</v>
       </c>
       <c r="D127" s="0">
-        <v>0.14149709956878032</v>
+        <v>0.011967439563205451</v>
       </c>
       <c r="E127" s="0">
-        <v>1.321127303841463</v>
+        <v>1.0750949525830755</v>
       </c>
       <c r="F127" s="0">
-        <v>0.0088000000000000005</v>
+        <v>0.043799999999999999</v>
       </c>
     </row>
     <row r="128">
@@ -2979,13 +2991,13 @@
         <v>0.48695084735205063</v>
       </c>
       <c r="D129" s="0">
-        <v>0.14460461644762601</v>
+        <v>0.14267371430877526</v>
       </c>
       <c r="E129" s="0">
-        <v>1.0213395741390696</v>
+        <v>1.0227685087125966</v>
       </c>
       <c r="F129" s="0">
-        <v>0.0045999999999999999</v>
+        <v>0.0044000000000000003</v>
       </c>
     </row>
     <row r="130">
@@ -2999,13 +3011,13 @@
         <v>0.25259167570440388</v>
       </c>
       <c r="D130" s="0">
-        <v>0.012481896368106538</v>
+        <v>0.010798657656116817</v>
       </c>
       <c r="E130" s="0">
-        <v>0.57496273571358492</v>
+        <v>0.57493024077123078</v>
       </c>
       <c r="F130" s="0">
-        <v>0.038399999999999997</v>
+        <v>0.041399999999999999</v>
       </c>
     </row>
     <row r="131">
@@ -3033,13 +3045,13 @@
         <v>0.22414674338064855</v>
       </c>
       <c r="D132" s="0">
-        <v>-0.0072189016766440184</v>
+        <v>-0.010084587197893652</v>
       </c>
       <c r="E132" s="0">
-        <v>0.51385955666366279</v>
+        <v>0.5128432034802094</v>
       </c>
       <c r="F132" s="0">
-        <v>0.056399999999999999</v>
+        <v>0.061600000000000002</v>
       </c>
     </row>
     <row r="133">
@@ -3053,13 +3065,13 @@
         <v>0.71155471729850139</v>
       </c>
       <c r="D133" s="0">
-        <v>0.29747923730929254</v>
+        <v>0.29229041699408215</v>
       </c>
       <c r="E133" s="0">
-        <v>1.2711377521778222</v>
+        <v>1.2574065919008197</v>
       </c>
       <c r="F133" s="0">
-        <v>0.0011999999999999999</v>
+        <v>0.0016000000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -3067,19 +3079,19 @@
         <v>2</v>
       </c>
       <c r="B134" s="0" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="C134" s="0">
-        <v>0.057242314887301193</v>
+        <v>0.24431012084032222</v>
       </c>
       <c r="D134" s="0">
-        <v>-0.24129721053023415</v>
+        <v>0.032033749045842608</v>
       </c>
       <c r="E134" s="0">
-        <v>0.34445967725290111</v>
+        <v>0.50640294686572007</v>
       </c>
       <c r="F134" s="0">
-        <v>0.69320000000000004</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="135">
@@ -3087,19 +3099,19 @@
         <v>2</v>
       </c>
       <c r="B135" s="0" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="C135" s="0">
-        <v>0.027915765266476378</v>
+        <v>0.23458970523140521</v>
       </c>
       <c r="D135" s="0">
-        <v>-0.26050317152389907</v>
+        <v>0.031276223456968677</v>
       </c>
       <c r="E135" s="0">
-        <v>0.30709426911352145</v>
+        <v>0.48721466350096954</v>
       </c>
       <c r="F135" s="0">
-        <v>0.83360000000000001</v>
+        <v>0.027199999999999999</v>
       </c>
     </row>
     <row r="136">
@@ -3107,19 +3119,19 @@
         <v>2</v>
       </c>
       <c r="B136" s="0" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="C136" s="0">
-        <v>0.15313799277571472</v>
+        <v>0.19498375031102633</v>
       </c>
       <c r="D136" s="0">
-        <v>-0.16081176885091958</v>
+        <v>-0.013111854138727452</v>
       </c>
       <c r="E136" s="0">
-        <v>0.47443548203144431</v>
+        <v>0.44462235799392336</v>
       </c>
       <c r="F136" s="0">
-        <v>0.33539999999999998</v>
+        <v>0.066600000000000007</v>
       </c>
     </row>
     <row r="137">
@@ -3127,19 +3139,19 @@
         <v>2</v>
       </c>
       <c r="B137" s="0" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="C137" s="0">
-        <v>0.10213176059422396</v>
+        <v>0.074602183410627187</v>
       </c>
       <c r="D137" s="0">
-        <v>-0.20407230518075439</v>
+        <v>-0.1781525348344708</v>
       </c>
       <c r="E137" s="0">
-        <v>0.40913104207702755</v>
+        <v>0.34174233546047117</v>
       </c>
       <c r="F137" s="0">
-        <v>0.54420000000000002</v>
+        <v>0.50419999999999998</v>
       </c>
     </row>
     <row r="138">
@@ -3167,13 +3179,13 @@
         <v>0.23435917164764675</v>
       </c>
       <c r="D139" s="0">
-        <v>0.05405372789379248</v>
+        <v>0.052533685357268822</v>
       </c>
       <c r="E139" s="0">
-        <v>0.52615971350551827</v>
+        <v>0.52410321862555698</v>
       </c>
       <c r="F139" s="0">
-        <v>0.010200000000000001</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="140">
@@ -3201,13 +3213,13 @@
         <v>0.26280410397140208</v>
       </c>
       <c r="D141" s="0">
-        <v>0.059446613774699897</v>
+        <v>0.056915248086072401</v>
       </c>
       <c r="E141" s="0">
-        <v>0.5884396596412147</v>
+        <v>0.59540681418278652</v>
       </c>
       <c r="F141" s="0">
-        <v>0.0091999999999999999</v>
+        <v>0.0061999999999999998</v>
       </c>
     </row>
     <row r="142">
@@ -3221,13 +3233,13 @@
         <v>0.22460386994645076</v>
       </c>
       <c r="D142" s="0">
-        <v>-0.54335349962053237</v>
+        <v>-0.53650951082908849</v>
       </c>
       <c r="E142" s="0">
-        <v>0.94372210471671214</v>
+        <v>0.91766617988628951</v>
       </c>
       <c r="F142" s="0">
-        <v>0.52300000000000002</v>
+        <v>0.53939999999999999</v>
       </c>
     </row>
     <row r="143">
@@ -3238,16 +3250,16 @@
         <v>55</v>
       </c>
       <c r="C143" s="0">
-        <v>0.54419316223935188</v>
+        <v>0.24264072651172841</v>
       </c>
       <c r="D143" s="0">
-        <v>0.24339487992169046</v>
+        <v>0.040414449012685205</v>
       </c>
       <c r="E143" s="0">
-        <v>1.0665404444426705</v>
+        <v>0.60529082218165897</v>
       </c>
       <c r="F143" s="0">
-        <v>0</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="144">
@@ -3258,16 +3270,16 @@
         <v>56</v>
       </c>
       <c r="C144" s="0">
-        <v>0.51486661261852706</v>
+        <v>0.25236114212064542</v>
       </c>
       <c r="D144" s="0">
-        <v>0.22445915634193922</v>
+        <v>0.046712500330396201</v>
       </c>
       <c r="E144" s="0">
-        <v>1.0298566505185378</v>
+        <v>0.61268856159845453</v>
       </c>
       <c r="F144" s="0">
-        <v>0</v>
+        <v>0.0089999999999999993</v>
       </c>
     </row>
     <row r="145">
@@ -3278,16 +3290,16 @@
         <v>57</v>
       </c>
       <c r="C145" s="0">
-        <v>0.64008884012776535</v>
+        <v>0.2919670970410243</v>
       </c>
       <c r="D145" s="0">
-        <v>0.28046673750937512</v>
+        <v>0.074789986285837023</v>
       </c>
       <c r="E145" s="0">
-        <v>1.2155481862073012</v>
+        <v>0.66356116817935029</v>
       </c>
       <c r="F145" s="0">
-        <v>0</v>
+        <v>0.0041999999999999998</v>
       </c>
     </row>
     <row r="146">
@@ -3298,16 +3310,16 @@
         <v>58</v>
       </c>
       <c r="C146" s="0">
-        <v>0.58908260794627454</v>
+        <v>0.41234866394142344</v>
       </c>
       <c r="D146" s="0">
-        <v>0.17723133446704179</v>
+        <v>0.022501902791680017</v>
       </c>
       <c r="E146" s="0">
-        <v>1.1881777745550068</v>
+        <v>0.94004154646315208</v>
       </c>
       <c r="F146" s="0">
-        <v>0.0047999999999999996</v>
+        <v>0.037400000000000003</v>
       </c>
     </row>
     <row r="147">
@@ -3349,13 +3361,13 @@
         <v>0.028444932323755334</v>
       </c>
       <c r="D149" s="0">
-        <v>-0.052489347441334544</v>
+        <v>-0.052949222994187195</v>
       </c>
       <c r="E149" s="0">
-        <v>0.12206473223656067</v>
+        <v>0.12452921456932192</v>
       </c>
       <c r="F149" s="0">
-        <v>0.4924</v>
+        <v>0.48020000000000002</v>
       </c>
     </row>
     <row r="150">
@@ -3369,13 +3381,13 @@
         <v>0.45896304159409751</v>
       </c>
       <c r="D150" s="0">
-        <v>-0.13328920312501669</v>
+        <v>-0.13248727792509213</v>
       </c>
       <c r="E150" s="0">
-        <v>1.1026016034186044</v>
+        <v>1.0875236792783687</v>
       </c>
       <c r="F150" s="0">
-        <v>0.1176</v>
+        <v>0.1268</v>
       </c>
     </row>
     <row r="151">
@@ -3386,16 +3398,16 @@
         <v>63</v>
       </c>
       <c r="C151" s="0">
-        <v>0.30983399059170508</v>
+        <v>0.0082815548640816639</v>
       </c>
       <c r="D151" s="0">
-        <v>0.10114685427556996</v>
+        <v>-0.09590265892057645</v>
       </c>
       <c r="E151" s="0">
-        <v>0.61864036433451852</v>
+        <v>0.15295442513291235</v>
       </c>
       <c r="F151" s="0">
-        <v>0.0028</v>
+        <v>0.89480000000000004</v>
       </c>
     </row>
     <row r="152">
@@ -3406,16 +3418,16 @@
         <v>110</v>
       </c>
       <c r="C152" s="0">
-        <v>0.28050744097088026</v>
+        <v>0.018001970472998674</v>
       </c>
       <c r="D152" s="0">
-        <v>0.079434594386959254</v>
+        <v>-0.069395951031515246</v>
       </c>
       <c r="E152" s="0">
-        <v>0.58341429656247423</v>
+        <v>0.15345568596791404</v>
       </c>
       <c r="F152" s="0">
-        <v>0.0057999999999999996</v>
+        <v>0.753</v>
       </c>
     </row>
     <row r="153">
@@ -3426,16 +3438,16 @@
         <v>111</v>
       </c>
       <c r="C153" s="0">
-        <v>0.4057296684801186</v>
+        <v>0.057607925393377557</v>
       </c>
       <c r="D153" s="0">
-        <v>0.14669414407503628</v>
+        <v>-0.015950708765589572</v>
       </c>
       <c r="E153" s="0">
-        <v>0.78243647196391519</v>
+        <v>0.179127692548885</v>
       </c>
       <c r="F153" s="0">
-        <v>0.0030000000000000001</v>
+        <v>0.13619999999999999</v>
       </c>
     </row>
     <row r="154">
@@ -3446,16 +3458,16 @@
         <v>66</v>
       </c>
       <c r="C154" s="0">
-        <v>0.35472343629862785</v>
+        <v>0.1779894922937767</v>
       </c>
       <c r="D154" s="0">
-        <v>0.040898176323758029</v>
+        <v>-0.097134728237698892</v>
       </c>
       <c r="E154" s="0">
-        <v>0.76677487220213425</v>
+        <v>0.50990600412165243</v>
       </c>
       <c r="F154" s="0">
-        <v>0.0276</v>
+        <v>0.2006</v>
       </c>
     </row>
     <row r="155">
@@ -3581,13 +3593,13 @@
         <v>0.48740797391785284</v>
       </c>
       <c r="D163" s="0">
-        <v>-0.075042485050014651</v>
+        <v>-0.078114210106990212</v>
       </c>
       <c r="E163" s="0">
-        <v>1.1238413119966935</v>
+        <v>1.1048498799423903</v>
       </c>
       <c r="F163" s="0">
-        <v>0.089599999999999999</v>
+        <v>0.095600000000000004</v>
       </c>
     </row>
     <row r="164">
@@ -3595,19 +3607,19 @@
         <v>2</v>
       </c>
       <c r="B164" s="0" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="C164" s="0">
-        <v>0.28138905826794974</v>
+        <v>0.02016337745967367</v>
       </c>
       <c r="D164" s="0">
-        <v>0.075944888131779992</v>
+        <v>-0.084832690482620987</v>
       </c>
       <c r="E164" s="0">
-        <v>0.56966511424349675</v>
+        <v>0.10576726663336017</v>
       </c>
       <c r="F164" s="0">
-        <v>0.0057999999999999996</v>
+        <v>0.66320000000000001</v>
       </c>
     </row>
     <row r="165">
@@ -3615,19 +3627,19 @@
         <v>2</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="C165" s="0">
-        <v>0.25206250864712493</v>
+        <v>0.01044296185075666</v>
       </c>
       <c r="D165" s="0">
-        <v>0.051128270698038908</v>
+        <v>-0.084528374788459648</v>
       </c>
       <c r="E165" s="0">
-        <v>0.53903082851571205</v>
+        <v>0.085898925066564838</v>
       </c>
       <c r="F165" s="0">
-        <v>0.0146</v>
+        <v>0.78879999999999995</v>
       </c>
     </row>
     <row r="166">
@@ -3638,16 +3650,16 @@
         <v>112</v>
       </c>
       <c r="C166" s="0">
-        <v>0.37728473615636327</v>
+        <v>0.029162993069622223</v>
       </c>
       <c r="D166" s="0">
-        <v>0.11603109457097949</v>
+        <v>-0.022128610506100113</v>
       </c>
       <c r="E166" s="0">
-        <v>0.74297120824832175</v>
+        <v>0.10625435395686927</v>
       </c>
       <c r="F166" s="0">
-        <v>0.0045999999999999999</v>
+        <v>0.28520000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -3658,16 +3670,16 @@
         <v>79</v>
       </c>
       <c r="C167" s="0">
-        <v>0.32627850397487251</v>
+        <v>0.14954455997002136</v>
       </c>
       <c r="D167" s="0">
-        <v>0.036815509064500096</v>
+        <v>-0.096829375799999007</v>
       </c>
       <c r="E167" s="0">
-        <v>0.70447361712595358</v>
+        <v>0.44366694163768261</v>
       </c>
       <c r="F167" s="0">
-        <v>0.0246</v>
+        <v>0.23280000000000001</v>
       </c>
     </row>
     <row r="168">
@@ -3692,16 +3704,16 @@
         <v>81</v>
       </c>
       <c r="C169" s="0">
-        <v>0.76879703218580264</v>
+        <v>0.46724459645817917</v>
       </c>
       <c r="D169" s="0">
-        <v>0.33666870472917554</v>
+        <v>-0.048850607804984125</v>
       </c>
       <c r="E169" s="0">
-        <v>1.3562941400831048</v>
+        <v>1.0569435108130039</v>
       </c>
       <c r="F169" s="0">
-        <v>0.00040000000000000002</v>
+        <v>0.077600000000000002</v>
       </c>
     </row>
     <row r="170">
@@ -3712,16 +3724,16 @@
         <v>82</v>
       </c>
       <c r="C170" s="0">
-        <v>0.73947048256497783</v>
+        <v>0.47696501206709618</v>
       </c>
       <c r="D170" s="0">
-        <v>0.30930807933645438</v>
+        <v>-0.041671372616878255</v>
       </c>
       <c r="E170" s="0">
-        <v>1.3275354710808982</v>
+        <v>1.071392211210743</v>
       </c>
       <c r="F170" s="0">
-        <v>0.00059999999999999995</v>
+        <v>0.075200000000000003</v>
       </c>
     </row>
     <row r="171">
@@ -3732,16 +3744,16 @@
         <v>83</v>
       </c>
       <c r="C171" s="0">
-        <v>0.86469271007421611</v>
+        <v>0.51657096698747507</v>
       </c>
       <c r="D171" s="0">
-        <v>0.42442615360409297</v>
+        <v>-0.0035982906490839017</v>
       </c>
       <c r="E171" s="0">
-        <v>1.4583851085685355</v>
+        <v>1.1089278841450294</v>
       </c>
       <c r="F171" s="0">
-        <v>0</v>
+        <v>0.050799999999999998</v>
       </c>
     </row>
     <row r="172">
@@ -3752,16 +3764,16 @@
         <v>84</v>
       </c>
       <c r="C172" s="0">
-        <v>0.8136864778927253</v>
+        <v>0.63695253388787421</v>
       </c>
       <c r="D172" s="0">
-        <v>0.39986332104364836</v>
+        <v>0.20877532232636448</v>
       </c>
       <c r="E172" s="0">
-        <v>1.3896382297967862</v>
+        <v>1.1863545993160387</v>
       </c>
       <c r="F172" s="0">
-        <v>0</v>
+        <v>0.0030000000000000001</v>
       </c>
     </row>
     <row r="173">
@@ -3783,19 +3795,19 @@
         <v>2</v>
       </c>
       <c r="B174" s="0" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="C174" s="0">
-        <v>0.029326549620824816</v>
+        <v>0.0097204156089170102</v>
       </c>
       <c r="D174" s="0">
-        <v>0.0047758563522511954</v>
+        <v>-0.029247364783438645</v>
       </c>
       <c r="E174" s="0">
-        <v>0.057123146888370058</v>
+        <v>0.053717566061795674</v>
       </c>
       <c r="F174" s="0">
-        <v>0.022200000000000001</v>
+        <v>0.6684</v>
       </c>
     </row>
     <row r="175">
@@ -3806,16 +3818,16 @@
         <v>114</v>
       </c>
       <c r="C175" s="0">
-        <v>0.095895677888413522</v>
+        <v>0.049326370529295893</v>
       </c>
       <c r="D175" s="0">
-        <v>-0.04347386119281154</v>
+        <v>-0.021171468289682638</v>
       </c>
       <c r="E175" s="0">
-        <v>0.25231604352984394</v>
+        <v>0.12883356396121287</v>
       </c>
       <c r="F175" s="0">
-        <v>0.1724</v>
+        <v>0.1608</v>
       </c>
     </row>
     <row r="176">
@@ -3826,16 +3838,16 @@
         <v>88</v>
       </c>
       <c r="C176" s="0">
-        <v>0.04488944570692277</v>
+        <v>0.16970793742969503</v>
       </c>
       <c r="D176" s="0">
-        <v>-0.24573633767601896</v>
+        <v>-0.068159171540960545</v>
       </c>
       <c r="E176" s="0">
-        <v>0.33874922334917512</v>
+        <v>0.42051970689938939</v>
       </c>
       <c r="F176" s="0">
-        <v>0.79459999999999997</v>
+        <v>0.1568</v>
       </c>
     </row>
     <row r="177">
@@ -3860,16 +3872,16 @@
         <v>115</v>
       </c>
       <c r="C178" s="0">
-        <v>0.12522222750923834</v>
+        <v>0.039605954920378883</v>
       </c>
       <c r="D178" s="0">
-        <v>-0.015594534096939505</v>
+        <v>-0.012283126594969329</v>
       </c>
       <c r="E178" s="0">
-        <v>0.28797268349721361</v>
+        <v>0.096159599251544936</v>
       </c>
       <c r="F178" s="0">
-        <v>0.080399999999999999</v>
+        <v>0.13039999999999999</v>
       </c>
     </row>
     <row r="179">
@@ -3880,16 +3892,16 @@
         <v>91</v>
       </c>
       <c r="C179" s="0">
-        <v>0.074215995327747586</v>
+        <v>0.15998752182077802</v>
       </c>
       <c r="D179" s="0">
-        <v>-0.22380084377057419</v>
+        <v>-0.071371796176583458</v>
       </c>
       <c r="E179" s="0">
-        <v>0.36890545241515316</v>
+        <v>0.40572142102439029</v>
       </c>
       <c r="F179" s="0">
-        <v>0.64439999999999997</v>
+        <v>0.16600000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -3911,19 +3923,19 @@
         <v>2</v>
       </c>
       <c r="B181" s="0" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C181" s="0">
-        <v>0.051006232181490752</v>
+        <v>0.12038156690039914</v>
       </c>
       <c r="D181" s="0">
-        <v>-0.25038085828327267</v>
+        <v>-0.11242861314251737</v>
       </c>
       <c r="E181" s="0">
-        <v>0.35716659812762486</v>
+        <v>0.37352684545858234</v>
       </c>
       <c r="F181" s="0">
-        <v>0.70240000000000002</v>
+        <v>0.29699999999999999</v>
       </c>
     </row>
     <row r="182">
@@ -3965,13 +3977,13 @@
         <v>0.95082611799984207</v>
       </c>
       <c r="D184" s="0">
-        <v>0.2615804762059965</v>
+        <v>0.26282498973765667</v>
       </c>
       <c r="E184" s="0">
-        <v>1.4528207717429862</v>
+        <v>1.4613152663511717</v>
       </c>
       <c r="F184" s="0">
-        <v>0.0050000000000000001</v>
+        <v>0.0067999999999999996</v>
       </c>
     </row>
     <row r="185">
@@ -3985,13 +3997,13 @@
         <v>0.70816954014023592</v>
       </c>
       <c r="D185" s="0">
-        <v>-0.049891448726698762</v>
+        <v>-0.081059454641293272</v>
       </c>
       <c r="E185" s="0">
-        <v>1.556992816205756</v>
+        <v>1.5459701928878962</v>
       </c>
       <c r="F185" s="0">
-        <v>0.065600000000000006</v>
+        <v>0.076999999999999999</v>
       </c>
     </row>
     <row r="186">
@@ -4005,13 +4017,13 @@
         <v>0.16002365123376067</v>
       </c>
       <c r="D186" s="0">
-        <v>-0.58835396885633984</v>
+        <v>-0.61859219175943747</v>
       </c>
       <c r="E186" s="0">
-        <v>0.6510585911742276</v>
+        <v>0.64604952596587029</v>
       </c>
       <c r="F186" s="0">
-        <v>0.75560000000000005</v>
+        <v>0.75039999999999996</v>
       </c>
     </row>
     <row r="187">
@@ -4025,13 +4037,13 @@
         <v>0.57938008496724014</v>
       </c>
       <c r="D187" s="0">
-        <v>-0.098663737753707348</v>
+        <v>-0.1303350445841874</v>
       </c>
       <c r="E187" s="0">
-        <v>1.2014011635763229</v>
+        <v>1.1901198863762317</v>
       </c>
       <c r="F187" s="0">
-        <v>0.096000000000000002</v>
+        <v>0.1048</v>
       </c>
     </row>
     <row r="188">
@@ -4045,13 +4057,13 @@
         <v>0.41778576453418254</v>
       </c>
       <c r="D188" s="0">
-        <v>-0.23378938826672441</v>
+        <v>-0.25650102794118668</v>
       </c>
       <c r="E188" s="0">
-        <v>0.94005176089252052</v>
+        <v>0.9278592044390046</v>
       </c>
       <c r="F188" s="0">
-        <v>0.22420000000000001</v>
+        <v>0.2346</v>
       </c>
     </row>
     <row r="189">
@@ -4079,13 +4091,13 @@
         <v>0.38417039461440933</v>
       </c>
       <c r="D190" s="0">
-        <v>-0.266808797762152</v>
+        <v>-0.2817678273151345</v>
       </c>
       <c r="E190" s="0">
-        <v>0.8836191043145305</v>
+        <v>0.86876102272143463</v>
       </c>
       <c r="F190" s="0">
-        <v>0.2742</v>
+        <v>0.27800000000000003</v>
       </c>
     </row>
     <row r="191">
@@ -4099,13 +4111,13 @@
         <v>0.88475687318617991</v>
       </c>
       <c r="D191" s="0">
-        <v>0.16639776967507103</v>
+        <v>0.17282000144890958</v>
       </c>
       <c r="E191" s="0">
-        <v>1.5412455415744699</v>
+        <v>1.520359915757679</v>
       </c>
       <c r="F191" s="0">
-        <v>0.0089999999999999993</v>
+        <v>0.0097999999999999997</v>
       </c>
     </row>
     <row r="192">
@@ -4116,16 +4128,16 @@
         <v>13</v>
       </c>
       <c r="C192" s="0">
-        <v>0.10278133634645958</v>
+        <v>0.404333772074083</v>
       </c>
       <c r="D192" s="0">
-        <v>-0.59200785440663717</v>
+        <v>-0.26504364034909678</v>
       </c>
       <c r="E192" s="0">
-        <v>0.53926862277838516</v>
+        <v>0.88307726520833185</v>
       </c>
       <c r="F192" s="0">
-        <v>0.85699999999999999</v>
+        <v>0.2646</v>
       </c>
     </row>
     <row r="193">
@@ -4136,16 +4148,16 @@
         <v>14</v>
       </c>
       <c r="C193" s="0">
-        <v>0.1321078859672844</v>
+        <v>0.39461335646516599</v>
       </c>
       <c r="D193" s="0">
-        <v>-0.56831846968356969</v>
+        <v>-0.27257611691623324</v>
       </c>
       <c r="E193" s="0">
-        <v>0.57406894121892194</v>
+        <v>0.85881088193209676</v>
       </c>
       <c r="F193" s="0">
-        <v>0.79039999999999999</v>
+        <v>0.26860000000000001</v>
       </c>
     </row>
     <row r="194">
@@ -4156,16 +4168,16 @@
         <v>15</v>
       </c>
       <c r="C194" s="0">
-        <v>0.0068856584580460622</v>
+        <v>0.35500740154478711</v>
       </c>
       <c r="D194" s="0">
-        <v>-0.69047586419287388</v>
+        <v>-0.31555525321668443</v>
       </c>
       <c r="E194" s="0">
-        <v>0.43406560349356249</v>
+        <v>0.82091686020491406</v>
       </c>
       <c r="F194" s="0">
-        <v>0.89359999999999995</v>
+        <v>0.32640000000000002</v>
       </c>
     </row>
     <row r="195">
@@ -4176,16 +4188,16 @@
         <v>16</v>
       </c>
       <c r="C195" s="0">
-        <v>0.057891890639536814</v>
+        <v>0.23462583464438797</v>
       </c>
       <c r="D195" s="0">
-        <v>-0.59883374696140212</v>
+        <v>-0.42557154809542264</v>
       </c>
       <c r="E195" s="0">
-        <v>0.46005766438161688</v>
+        <v>0.64018001843672745</v>
       </c>
       <c r="F195" s="0">
-        <v>0.9526</v>
+        <v>0.53239999999999999</v>
       </c>
     </row>
     <row r="196">
@@ -4213,10 +4225,10 @@
         <v>0.24265657785960615</v>
       </c>
       <c r="D197" s="0">
-        <v>-0.60589105416758493</v>
+        <v>-0.57975331383069828</v>
       </c>
       <c r="E197" s="0">
-        <v>0.84154724086844679</v>
+        <v>0.84406365206092948</v>
       </c>
       <c r="F197" s="0">
         <v>0.59319999999999995</v>
@@ -4233,10 +4245,10 @@
         <v>0.79080246676608135</v>
       </c>
       <c r="D198" s="0">
-        <v>0.46347369746351341</v>
+        <v>0.46810143561417511</v>
       </c>
       <c r="E198" s="0">
-        <v>1.2094579161767922</v>
+        <v>1.2251162983307458</v>
       </c>
       <c r="F198" s="0">
         <v>0</v>
@@ -4253,10 +4265,10 @@
         <v>0.37144603303260193</v>
       </c>
       <c r="D199" s="0">
-        <v>-0.25335348220976683</v>
+        <v>-0.24003381703665583</v>
       </c>
       <c r="E199" s="0">
-        <v>0.87057025982795144</v>
+        <v>0.8834246359477036</v>
       </c>
       <c r="F199" s="0">
         <v>0.20799999999999999</v>
@@ -4273,13 +4285,13 @@
         <v>0.53304035346565948</v>
       </c>
       <c r="D200" s="0">
-        <v>0.074631801304191114</v>
+        <v>0.070433502325638386</v>
       </c>
       <c r="E200" s="0">
-        <v>0.99022596504128968</v>
+        <v>1.0005710672146013</v>
       </c>
       <c r="F200" s="0">
-        <v>0.0276</v>
+        <v>0.0224</v>
       </c>
     </row>
     <row r="201">
@@ -4307,13 +4319,13 @@
         <v>0.56665572338543269</v>
       </c>
       <c r="D202" s="0">
-        <v>0.14848399996471418</v>
+        <v>0.14781101929422247</v>
       </c>
       <c r="E202" s="0">
-        <v>1.0078693377529979</v>
+        <v>1.0191881856032083</v>
       </c>
       <c r="F202" s="0">
-        <v>0.010800000000000001</v>
+        <v>0.0070000000000000001</v>
       </c>
     </row>
     <row r="203">
@@ -4327,13 +4339,13 @@
         <v>0.066069244813662165</v>
       </c>
       <c r="D203" s="0">
-        <v>-0.51806063253958912</v>
+        <v>-0.49465929620931048</v>
       </c>
       <c r="E203" s="0">
-        <v>0.58897824064450477</v>
+        <v>0.5983607877860494</v>
       </c>
       <c r="F203" s="0">
-        <v>0.81679999999999997</v>
+        <v>0.80620000000000003</v>
       </c>
     </row>
     <row r="204">
@@ -4344,16 +4356,16 @@
         <v>25</v>
       </c>
       <c r="C204" s="0">
-        <v>0.84804478165338249</v>
+        <v>0.54649234592575902</v>
       </c>
       <c r="D204" s="0">
-        <v>0.47827003775673149</v>
+        <v>0.18566192859265812</v>
       </c>
       <c r="E204" s="0">
-        <v>1.3036243279805317</v>
+        <v>0.95711618631626139</v>
       </c>
       <c r="F204" s="0">
-        <v>0</v>
+        <v>0.0030000000000000001</v>
       </c>
     </row>
     <row r="205">
@@ -4364,16 +4376,16 @@
         <v>26</v>
       </c>
       <c r="C205" s="0">
-        <v>0.81871823203255767</v>
+        <v>0.55621276153467603</v>
       </c>
       <c r="D205" s="0">
-        <v>0.44978656509686948</v>
+        <v>0.19797686102032852</v>
       </c>
       <c r="E205" s="0">
-        <v>1.2737331575000457</v>
+        <v>0.96672038670308513</v>
       </c>
       <c r="F205" s="0">
-        <v>0</v>
+        <v>0.0023999999999999998</v>
       </c>
     </row>
     <row r="206">
@@ -4384,16 +4396,16 @@
         <v>27</v>
       </c>
       <c r="C206" s="0">
-        <v>0.94394045954179595</v>
+        <v>0.59581871645505491</v>
       </c>
       <c r="D206" s="0">
-        <v>0.56153545764943325</v>
+        <v>0.22735835131849885</v>
       </c>
       <c r="E206" s="0">
-        <v>1.4072059605389071</v>
+        <v>1.023228701450714</v>
       </c>
       <c r="F206" s="0">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="207">
@@ -4404,13 +4416,13 @@
         <v>28</v>
       </c>
       <c r="C207" s="0">
-        <v>0.89293422736030514</v>
+        <v>0.71620028335545405</v>
       </c>
       <c r="D207" s="0">
-        <v>0.5378380326940303</v>
+        <v>0.37128569016966667</v>
       </c>
       <c r="E207" s="0">
-        <v>1.3375346590187487</v>
+        <v>1.1584545606114658</v>
       </c>
       <c r="F207" s="0">
         <v>0</v>
@@ -4441,13 +4453,13 @@
         <v>0.5481458889064752</v>
       </c>
       <c r="D209" s="0">
-        <v>0.18546008179816378</v>
+        <v>0.18777323607541685</v>
       </c>
       <c r="E209" s="0">
-        <v>1.2240896495775675</v>
+        <v>1.1941478333751216</v>
       </c>
       <c r="F209" s="0">
-        <v>0.001</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="210">
@@ -4461,13 +4473,13 @@
         <v>0.12878945517299578</v>
       </c>
       <c r="D210" s="0">
-        <v>-0.21613171235374834</v>
+        <v>-0.21645619317407405</v>
       </c>
       <c r="E210" s="0">
-        <v>0.70659002533073823</v>
+        <v>0.70581594604433295</v>
       </c>
       <c r="F210" s="0">
-        <v>0.44879999999999998</v>
+        <v>0.44679999999999998</v>
       </c>
     </row>
     <row r="211">
@@ -4481,13 +4493,13 @@
         <v>0.29038377560605333</v>
       </c>
       <c r="D211" s="0">
-        <v>-0.00097593372163740089</v>
+        <v>-0.0015387094667645984</v>
       </c>
       <c r="E211" s="0">
-        <v>0.87954374159073589</v>
+        <v>0.85669360990150412</v>
       </c>
       <c r="F211" s="0">
-        <v>0.050799999999999998</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="212">
@@ -4515,13 +4527,13 @@
         <v>0.32399914552582654</v>
       </c>
       <c r="D213" s="0">
-        <v>0.006015468145879832</v>
+        <v>0.0087601578031862859</v>
       </c>
       <c r="E213" s="0">
-        <v>0.94542925123116905</v>
+        <v>0.91742544763963774</v>
       </c>
       <c r="F213" s="0">
-        <v>0.045999999999999999</v>
+        <v>0.045199999999999997</v>
       </c>
     </row>
     <row r="214">
@@ -4535,13 +4547,13 @@
         <v>0.17658733304594398</v>
       </c>
       <c r="D214" s="0">
-        <v>-0.76941314305374486</v>
+        <v>-0.77778419779901165</v>
       </c>
       <c r="E214" s="0">
-        <v>0.9802234082445821</v>
+        <v>0.97200087152446724</v>
       </c>
       <c r="F214" s="0">
-        <v>0.74119999999999997</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="215">
@@ -4552,16 +4564,16 @@
         <v>36</v>
       </c>
       <c r="C215" s="0">
-        <v>0.60538820379377634</v>
+        <v>0.30383576806615287</v>
       </c>
       <c r="D215" s="0">
-        <v>0.21000847553793758</v>
+        <v>-0.024776669754562886</v>
       </c>
       <c r="E215" s="0">
-        <v>1.3391639189020641</v>
+        <v>0.92823665357922491</v>
       </c>
       <c r="F215" s="0">
-        <v>0.0025999999999999999</v>
+        <v>0.076200000000000004</v>
       </c>
     </row>
     <row r="216">
@@ -4572,16 +4584,16 @@
         <v>37</v>
       </c>
       <c r="C216" s="0">
-        <v>0.57606165417295152</v>
+        <v>0.31355618367506988</v>
       </c>
       <c r="D216" s="0">
-        <v>0.18816924920012645</v>
+        <v>-0.0073443121505430975</v>
       </c>
       <c r="E216" s="0">
-        <v>1.3058828271739997</v>
+        <v>0.93337538413748722</v>
       </c>
       <c r="F216" s="0">
-        <v>0.0032000000000000002</v>
+        <v>0.056000000000000001</v>
       </c>
     </row>
     <row r="217">
@@ -4592,16 +4604,16 @@
         <v>38</v>
       </c>
       <c r="C217" s="0">
-        <v>0.7012838816821898</v>
+        <v>0.35316213859544876</v>
       </c>
       <c r="D217" s="0">
-        <v>0.28489299402845658</v>
+        <v>0.03826163991335943</v>
       </c>
       <c r="E217" s="0">
-        <v>1.4466357507686132</v>
+        <v>0.96422299250689869</v>
       </c>
       <c r="F217" s="0">
-        <v>0.00059999999999999995</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="218">
@@ -4612,16 +4624,16 @@
         <v>39</v>
       </c>
       <c r="C218" s="0">
-        <v>0.650277649500699</v>
+        <v>0.4735437054958479</v>
       </c>
       <c r="D218" s="0">
-        <v>0.17122202620925386</v>
+        <v>0.033687660940213249</v>
       </c>
       <c r="E218" s="0">
-        <v>1.4850490403799275</v>
+        <v>1.2042145358919238</v>
       </c>
       <c r="F218" s="0">
-        <v>0.0064000000000000003</v>
+        <v>0.033399999999999999</v>
       </c>
     </row>
     <row r="219">
@@ -4649,13 +4661,13 @@
         <v>0.41935643373347942</v>
       </c>
       <c r="D220" s="0">
-        <v>0.1085449207053456</v>
+        <v>0.11006665116714667</v>
       </c>
       <c r="E220" s="0">
-        <v>0.92232896944597465</v>
+        <v>0.91152761668186388</v>
       </c>
       <c r="F220" s="0">
-        <v>0.0066</v>
+        <v>0.0057999999999999996</v>
       </c>
     </row>
     <row r="221">
@@ -4669,13 +4681,13 @@
         <v>0.25776211330042187</v>
       </c>
       <c r="D221" s="0">
-        <v>0.020165153469423422</v>
+        <v>0.019197791075058562</v>
       </c>
       <c r="E221" s="0">
-        <v>0.58430222723894421</v>
+        <v>0.58237831961873776</v>
       </c>
       <c r="F221" s="0">
-        <v>0.030800000000000001</v>
+        <v>0.031199999999999999</v>
       </c>
     </row>
     <row r="222">
@@ -4703,13 +4715,13 @@
         <v>0.22414674338064866</v>
       </c>
       <c r="D223" s="0">
-        <v>-0.0072189016766439074</v>
+        <v>-0.010084587197893652</v>
       </c>
       <c r="E223" s="0">
-        <v>0.51385955666366279</v>
+        <v>0.5128432034802094</v>
       </c>
       <c r="F223" s="0">
-        <v>0.056399999999999999</v>
+        <v>0.061600000000000002</v>
       </c>
     </row>
     <row r="224">
@@ -4723,13 +4735,13 @@
         <v>0.72473322195241918</v>
       </c>
       <c r="D224" s="0">
-        <v>0.30128099653230583</v>
+        <v>0.29614354575660717</v>
       </c>
       <c r="E224" s="0">
-        <v>1.2845968684306295</v>
+        <v>1.2717916219159213</v>
       </c>
       <c r="F224" s="0">
-        <v>0.001</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="225">
@@ -4737,19 +4749,19 @@
         <v>3</v>
       </c>
       <c r="B225" s="0" t="s">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="C225" s="0">
-        <v>0.057242314887301082</v>
+        <v>0.24431012084032233</v>
       </c>
       <c r="D225" s="0">
-        <v>-0.24129721053023401</v>
+        <v>0.032033749045842552</v>
       </c>
       <c r="E225" s="0">
-        <v>0.34445967725290111</v>
+        <v>0.50640294686571985</v>
       </c>
       <c r="F225" s="0">
-        <v>0.69320000000000004</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="226">
@@ -4757,19 +4769,19 @@
         <v>3</v>
       </c>
       <c r="B226" s="0" t="s">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="C226" s="0">
-        <v>0.027915765266476267</v>
+        <v>0.23458970523140532</v>
       </c>
       <c r="D226" s="0">
-        <v>-0.26050317152389913</v>
+        <v>0.031276223456968621</v>
       </c>
       <c r="E226" s="0">
-        <v>0.30709426911352167</v>
+        <v>0.48721466350096942</v>
       </c>
       <c r="F226" s="0">
-        <v>0.83360000000000001</v>
+        <v>0.027199999999999999</v>
       </c>
     </row>
     <row r="227">
@@ -4777,19 +4789,19 @@
         <v>3</v>
       </c>
       <c r="B227" s="0" t="s">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="C227" s="0">
-        <v>0.1531379927757146</v>
+        <v>0.19498375031102644</v>
       </c>
       <c r="D227" s="0">
-        <v>-0.16081176885091969</v>
+        <v>-0.01311185413872723</v>
       </c>
       <c r="E227" s="0">
-        <v>0.47443548203144459</v>
+        <v>0.44462235799392325</v>
       </c>
       <c r="F227" s="0">
-        <v>0.33539999999999998</v>
+        <v>0.066600000000000007</v>
       </c>
     </row>
     <row r="228">
@@ -4797,19 +4809,19 @@
         <v>3</v>
       </c>
       <c r="B228" s="0" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="C228" s="0">
-        <v>0.10213176059422385</v>
+        <v>0.074602183410627299</v>
       </c>
       <c r="D228" s="0">
-        <v>-0.20407230518075434</v>
+        <v>-0.17815253483447085</v>
       </c>
       <c r="E228" s="0">
-        <v>0.40913104207702772</v>
+        <v>0.34174233546047128</v>
       </c>
       <c r="F228" s="0">
-        <v>0.54420000000000002</v>
+        <v>0.50419999999999998</v>
       </c>
     </row>
     <row r="229">
@@ -4837,13 +4849,13 @@
         <v>0.16159432043305755</v>
       </c>
       <c r="D230" s="0">
-        <v>-0.033567220359445205</v>
+        <v>-0.03309156203350222</v>
       </c>
       <c r="E230" s="0">
-        <v>0.44991073274856719</v>
+        <v>0.44692129680156695</v>
       </c>
       <c r="F230" s="0">
-        <v>0.1012</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="231">
@@ -4871,13 +4883,13 @@
         <v>0.19520969035283076</v>
       </c>
       <c r="D232" s="0">
-        <v>-0.011730693820518778</v>
+        <v>-0.014495913407339855</v>
       </c>
       <c r="E232" s="0">
-        <v>0.51367976284253669</v>
+        <v>0.50751060790452973</v>
       </c>
       <c r="F232" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.064799999999999997</v>
       </c>
     </row>
     <row r="233">
@@ -4891,13 +4903,13 @@
         <v>0.30537678821893977</v>
       </c>
       <c r="D233" s="0">
-        <v>-0.46394279529064464</v>
+        <v>-0.46597360657860271</v>
       </c>
       <c r="E233" s="0">
-        <v>1.0315913877034077</v>
+        <v>1.0196764859741032</v>
       </c>
       <c r="F233" s="0">
-        <v>0.39360000000000001</v>
+        <v>0.40620000000000001</v>
       </c>
     </row>
     <row r="234">
@@ -4908,16 +4920,16 @@
         <v>55</v>
       </c>
       <c r="C234" s="0">
-        <v>0.4765987486207805</v>
+        <v>0.17504631289315709</v>
       </c>
       <c r="D234" s="0">
-        <v>0.18068588864213819</v>
+        <v>-0.033388346364232047</v>
       </c>
       <c r="E234" s="0">
-        <v>0.9706752372598132</v>
+        <v>0.52035295821535854</v>
       </c>
       <c r="F234" s="0">
-        <v>0.0025999999999999999</v>
+        <v>0.1002</v>
       </c>
     </row>
     <row r="235">
@@ -4928,16 +4940,16 @@
         <v>56</v>
       </c>
       <c r="C235" s="0">
-        <v>0.44727219899995568</v>
+        <v>0.1847667285020741</v>
       </c>
       <c r="D235" s="0">
-        <v>0.16010440014344105</v>
+        <v>-0.022802611755584068</v>
       </c>
       <c r="E235" s="0">
-        <v>0.93910519419270044</v>
+        <v>0.52731719551130274</v>
       </c>
       <c r="F235" s="0">
-        <v>0.0028</v>
+        <v>0.084599999999999995</v>
       </c>
     </row>
     <row r="236">
@@ -4948,16 +4960,16 @@
         <v>57</v>
       </c>
       <c r="C236" s="0">
-        <v>0.57249442650919402</v>
+        <v>0.22437268342245298</v>
       </c>
       <c r="D236" s="0">
-        <v>0.22719196374119299</v>
+        <v>0.0075705474003782414</v>
       </c>
       <c r="E236" s="0">
-        <v>1.1224470848025505</v>
+        <v>0.57492871542629187</v>
       </c>
       <c r="F236" s="0">
-        <v>0</v>
+        <v>0.043200000000000002</v>
       </c>
     </row>
     <row r="237">
@@ -4968,16 +4980,16 @@
         <v>58</v>
       </c>
       <c r="C237" s="0">
-        <v>0.52148819432770321</v>
+        <v>0.34475425032285212</v>
       </c>
       <c r="D237" s="0">
-        <v>0.11414831159237349</v>
+        <v>-0.036144214277908315</v>
       </c>
       <c r="E237" s="0">
-        <v>1.1086486794028803</v>
+        <v>0.86470690556202945</v>
       </c>
       <c r="F237" s="0">
-        <v>0.0112</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="238">
@@ -5019,13 +5031,13 @@
         <v>0.033615369919773208</v>
       </c>
       <c r="D240" s="0">
-        <v>-0.03897636498775392</v>
+        <v>-0.036979769969737453</v>
       </c>
       <c r="E240" s="0">
-        <v>0.12198446101217983</v>
+        <v>0.12466378022860469</v>
       </c>
       <c r="F240" s="0">
-        <v>0.3448</v>
+        <v>0.34660000000000002</v>
       </c>
     </row>
     <row r="241">
@@ -5039,13 +5051,13 @@
         <v>0.46697110865199731</v>
       </c>
       <c r="D241" s="0">
-        <v>-0.14884379094142369</v>
+        <v>-0.15776023934148698</v>
       </c>
       <c r="E241" s="0">
-        <v>1.1336988962327124</v>
+        <v>1.1272678482238958</v>
       </c>
       <c r="F241" s="0">
-        <v>0.1278</v>
+        <v>0.1404</v>
       </c>
     </row>
     <row r="242">
@@ -5056,16 +5068,16 @@
         <v>63</v>
       </c>
       <c r="C242" s="0">
-        <v>0.31500442818772295</v>
+        <v>0.013451992460099538</v>
       </c>
       <c r="D242" s="0">
-        <v>0.1084654206142644</v>
+        <v>-0.098824316248154409</v>
       </c>
       <c r="E242" s="0">
-        <v>0.62527098048548635</v>
+        <v>0.17141162321179126</v>
       </c>
       <c r="F242" s="0">
-        <v>0.0014</v>
+        <v>0.82599999999999996</v>
       </c>
     </row>
     <row r="243">
@@ -5076,16 +5088,16 @@
         <v>110</v>
       </c>
       <c r="C243" s="0">
-        <v>0.28567787856689814</v>
+        <v>0.023172408069016548</v>
       </c>
       <c r="D243" s="0">
-        <v>0.0864111170531002</v>
+        <v>-0.072524931165182105</v>
       </c>
       <c r="E243" s="0">
-        <v>0.59077124174852647</v>
+        <v>0.16744432893042288</v>
       </c>
       <c r="F243" s="0">
-        <v>0.0030000000000000001</v>
+        <v>0.68500000000000005</v>
       </c>
     </row>
     <row r="244">
@@ -5096,16 +5108,16 @@
         <v>111</v>
       </c>
       <c r="C244" s="0">
-        <v>0.41090010607613647</v>
+        <v>0.062778362989395431</v>
       </c>
       <c r="D244" s="0">
-        <v>0.15078144113714231</v>
+        <v>-0.010514536212595377</v>
       </c>
       <c r="E244" s="0">
-        <v>0.78185593190539282</v>
+        <v>0.19011418403361569</v>
       </c>
       <c r="F244" s="0">
-        <v>0.0016000000000000001</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="245">
@@ -5116,16 +5128,16 @@
         <v>66</v>
       </c>
       <c r="C245" s="0">
-        <v>0.35989387389464572</v>
+        <v>0.18315992988979457</v>
       </c>
       <c r="D245" s="0">
-        <v>0.043486213754006561</v>
+        <v>-0.08708329397219905</v>
       </c>
       <c r="E245" s="0">
-        <v>0.78197442130196559</v>
+        <v>0.5250775111658823</v>
       </c>
       <c r="F245" s="0">
-        <v>0.023199999999999999</v>
+        <v>0.18859999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -5251,13 +5263,13 @@
         <v>0.50058647857177052</v>
       </c>
       <c r="D254" s="0">
-        <v>-0.072067819904726882</v>
+        <v>-0.080563757821304538</v>
       </c>
       <c r="E254" s="0">
-        <v>1.1487519657751417</v>
+        <v>1.1382476988498569</v>
       </c>
       <c r="F254" s="0">
-        <v>0.0872</v>
+        <v>0.094600000000000004</v>
       </c>
     </row>
     <row r="255">
@@ -5265,19 +5277,19 @@
         <v>3</v>
       </c>
       <c r="B255" s="0" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="C255" s="0">
-        <v>0.28138905826794974</v>
+        <v>0.02016337745967367</v>
       </c>
       <c r="D255" s="0">
-        <v>0.075944888131779992</v>
+        <v>-0.084832690482620987</v>
       </c>
       <c r="E255" s="0">
-        <v>0.56966511424349675</v>
+        <v>0.10576726663336017</v>
       </c>
       <c r="F255" s="0">
-        <v>0.0057999999999999996</v>
+        <v>0.66320000000000001</v>
       </c>
     </row>
     <row r="256">
@@ -5285,19 +5297,19 @@
         <v>3</v>
       </c>
       <c r="B256" s="0" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="C256" s="0">
-        <v>0.25206250864712493</v>
+        <v>0.01044296185075666</v>
       </c>
       <c r="D256" s="0">
-        <v>0.051128270698038908</v>
+        <v>-0.084528374788459648</v>
       </c>
       <c r="E256" s="0">
-        <v>0.53903082851571205</v>
+        <v>0.085898925066564838</v>
       </c>
       <c r="F256" s="0">
-        <v>0.0146</v>
+        <v>0.78879999999999995</v>
       </c>
     </row>
     <row r="257">
@@ -5308,16 +5320,16 @@
         <v>112</v>
       </c>
       <c r="C257" s="0">
-        <v>0.37728473615636327</v>
+        <v>0.029162993069622223</v>
       </c>
       <c r="D257" s="0">
-        <v>0.11603109457097949</v>
+        <v>-0.022128610506100113</v>
       </c>
       <c r="E257" s="0">
-        <v>0.74297120824832175</v>
+        <v>0.10625435395686927</v>
       </c>
       <c r="F257" s="0">
-        <v>0.0045999999999999999</v>
+        <v>0.28520000000000001</v>
       </c>
     </row>
     <row r="258">
@@ -5328,16 +5340,16 @@
         <v>79</v>
       </c>
       <c r="C258" s="0">
-        <v>0.32627850397487251</v>
+        <v>0.14954455997002136</v>
       </c>
       <c r="D258" s="0">
-        <v>0.036815509064500096</v>
+        <v>-0.096829375799999007</v>
       </c>
       <c r="E258" s="0">
-        <v>0.70447361712595358</v>
+        <v>0.44366694163768261</v>
       </c>
       <c r="F258" s="0">
-        <v>0.0246</v>
+        <v>0.23280000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -5362,16 +5374,16 @@
         <v>81</v>
       </c>
       <c r="C260" s="0">
-        <v>0.78197553683972032</v>
+        <v>0.48042310111209685</v>
       </c>
       <c r="D260" s="0">
-        <v>0.34103838360276839</v>
+        <v>-0.047396300410559034</v>
       </c>
       <c r="E260" s="0">
-        <v>1.3839289484374566</v>
+        <v>1.0860852371084588</v>
       </c>
       <c r="F260" s="0">
-        <v>0.00040000000000000002</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="261">
@@ -5382,16 +5394,16 @@
         <v>82</v>
       </c>
       <c r="C261" s="0">
-        <v>0.7526489872188955</v>
+        <v>0.49014351672101386</v>
       </c>
       <c r="D261" s="0">
-        <v>0.31563988021993167</v>
+        <v>-0.040364302937567764</v>
       </c>
       <c r="E261" s="0">
-        <v>1.3538337913360325</v>
+        <v>1.0982765248194217</v>
       </c>
       <c r="F261" s="0">
-        <v>0.00059999999999999995</v>
+        <v>0.072800000000000004</v>
       </c>
     </row>
     <row r="262">
@@ -5402,16 +5414,16 @@
         <v>83</v>
       </c>
       <c r="C262" s="0">
-        <v>0.87787121472813379</v>
+        <v>0.52974947164139275</v>
       </c>
       <c r="D262" s="0">
-        <v>0.43503931313879973</v>
+        <v>0.0015569584364473199</v>
       </c>
       <c r="E262" s="0">
-        <v>1.4782130182074327</v>
+        <v>1.1405597175171196</v>
       </c>
       <c r="F262" s="0">
-        <v>0</v>
+        <v>0.049000000000000002</v>
       </c>
     </row>
     <row r="263">
@@ -5422,16 +5434,16 @@
         <v>84</v>
       </c>
       <c r="C263" s="0">
-        <v>0.82686498254664298</v>
+        <v>0.65013103854179188</v>
       </c>
       <c r="D263" s="0">
-        <v>0.41118332090336474</v>
+        <v>0.22125323933129387</v>
       </c>
       <c r="E263" s="0">
-        <v>1.3973681191216492</v>
+        <v>1.1955880548798312</v>
       </c>
       <c r="F263" s="0">
-        <v>0</v>
+        <v>0.0022000000000000001</v>
       </c>
     </row>
     <row r="264">
@@ -5453,19 +5465,19 @@
         <v>3</v>
       </c>
       <c r="B265" s="0" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="C265" s="0">
-        <v>0.029326549620824816</v>
+        <v>0.0097204156089170102</v>
       </c>
       <c r="D265" s="0">
-        <v>0.0047758563522511954</v>
+        <v>-0.029247364783438645</v>
       </c>
       <c r="E265" s="0">
-        <v>0.057123146888370058</v>
+        <v>0.053717566061795674</v>
       </c>
       <c r="F265" s="0">
-        <v>0.022200000000000001</v>
+        <v>0.6684</v>
       </c>
     </row>
     <row r="266">
@@ -5476,16 +5488,16 @@
         <v>114</v>
       </c>
       <c r="C266" s="0">
-        <v>0.095895677888413522</v>
+        <v>0.049326370529295893</v>
       </c>
       <c r="D266" s="0">
-        <v>-0.04347386119281154</v>
+        <v>-0.021171468289682638</v>
       </c>
       <c r="E266" s="0">
-        <v>0.25231604352984394</v>
+        <v>0.12883356396121287</v>
       </c>
       <c r="F266" s="0">
-        <v>0.1724</v>
+        <v>0.1608</v>
       </c>
     </row>
     <row r="267">
@@ -5496,16 +5508,16 @@
         <v>88</v>
       </c>
       <c r="C267" s="0">
-        <v>0.04488944570692277</v>
+        <v>0.16970793742969503</v>
       </c>
       <c r="D267" s="0">
-        <v>-0.24573633767601896</v>
+        <v>-0.068159171540960545</v>
       </c>
       <c r="E267" s="0">
-        <v>0.33874922334917512</v>
+        <v>0.42051970689938939</v>
       </c>
       <c r="F267" s="0">
-        <v>0.79459999999999997</v>
+        <v>0.1568</v>
       </c>
     </row>
     <row r="268">
@@ -5530,16 +5542,16 @@
         <v>115</v>
       </c>
       <c r="C269" s="0">
-        <v>0.12522222750923834</v>
+        <v>0.039605954920378883</v>
       </c>
       <c r="D269" s="0">
-        <v>-0.015594534096939505</v>
+        <v>-0.012283126594969329</v>
       </c>
       <c r="E269" s="0">
-        <v>0.28797268349721361</v>
+        <v>0.096159599251544936</v>
       </c>
       <c r="F269" s="0">
-        <v>0.080399999999999999</v>
+        <v>0.13039999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -5550,16 +5562,16 @@
         <v>91</v>
       </c>
       <c r="C270" s="0">
-        <v>0.074215995327747586</v>
+        <v>0.15998752182077802</v>
       </c>
       <c r="D270" s="0">
-        <v>-0.22380084377057419</v>
+        <v>-0.071371796176583458</v>
       </c>
       <c r="E270" s="0">
-        <v>0.36890545241515316</v>
+        <v>0.40572142102439029</v>
       </c>
       <c r="F270" s="0">
-        <v>0.64439999999999997</v>
+        <v>0.16600000000000001</v>
       </c>
     </row>
     <row r="271">
@@ -5581,19 +5593,19 @@
         <v>3</v>
       </c>
       <c r="B272" s="0" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C272" s="0">
-        <v>0.051006232181490752</v>
+        <v>0.12038156690039914</v>
       </c>
       <c r="D272" s="0">
-        <v>-0.25038085828327267</v>
+        <v>-0.11242861314251737</v>
       </c>
       <c r="E272" s="0">
-        <v>0.35716659812762486</v>
+        <v>0.37352684545858234</v>
       </c>
       <c r="F272" s="0">
-        <v>0.70240000000000002</v>
+        <v>0.29699999999999999</v>
       </c>
     </row>
     <row r="273">
